--- a/лаб.xlsx
+++ b/лаб.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="139">
   <si>
     <t>Имя</t>
   </si>
@@ -75,78 +75,6 @@
     <t>13.15.2021</t>
   </si>
   <si>
-    <t>Завьялова Алисия Артёмовна</t>
-  </si>
-  <si>
-    <t>Клюев Иван Максимович</t>
-  </si>
-  <si>
-    <t>Васильев Артур Ильич</t>
-  </si>
-  <si>
-    <t>Шмелев Константин Кириллович</t>
-  </si>
-  <si>
-    <t>Матвеева Марьям Платоновна</t>
-  </si>
-  <si>
-    <t>Кольцова Варвара Максимовна</t>
-  </si>
-  <si>
-    <t>Кочеткова Диана Дмитриевна</t>
-  </si>
-  <si>
-    <t>Малышева Василиса Максимовна</t>
-  </si>
-  <si>
-    <t>Кузнецов Александр Артёмович</t>
-  </si>
-  <si>
-    <t>Александров Юрий Александрович</t>
-  </si>
-  <si>
-    <t>Харитонова Ксения Егоровна</t>
-  </si>
-  <si>
-    <t>Дроздова Марьяна Степановна</t>
-  </si>
-  <si>
-    <t>Быков Илья Иванович</t>
-  </si>
-  <si>
-    <t>Тарасов Артём Артёмович</t>
-  </si>
-  <si>
-    <t>Смирнова Вероника Максимовна</t>
-  </si>
-  <si>
-    <t>Корнилова Арина Мироновна</t>
-  </si>
-  <si>
-    <t>Макарова Алиса Ивановна</t>
-  </si>
-  <si>
-    <t>Рубцова Александра Арсентьевна</t>
-  </si>
-  <si>
-    <t>Соболева Ева Семёновна</t>
-  </si>
-  <si>
-    <t>Большаков Богдан Богданович</t>
-  </si>
-  <si>
-    <t>Лаврентьева Ольга Владимировна</t>
-  </si>
-  <si>
-    <t>Воробьева Полина Дмитриевна</t>
-  </si>
-  <si>
-    <t>Захарова Ева Тихоновна</t>
-  </si>
-  <si>
-    <t>Трофимова Софья Марковна</t>
-  </si>
-  <si>
     <t>Симонова</t>
   </si>
   <si>
@@ -340,6 +268,171 @@
   </si>
   <si>
     <t xml:space="preserve">Тихонова  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Завьялова  </t>
+  </si>
+  <si>
+    <t>Алисия</t>
+  </si>
+  <si>
+    <t>Максимович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Клюев  </t>
+  </si>
+  <si>
+    <t>Ильич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Васильев  </t>
+  </si>
+  <si>
+    <t>Артур</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шмелев  </t>
+  </si>
+  <si>
+    <t>Константин</t>
+  </si>
+  <si>
+    <t>Платоновна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Матвеева  </t>
+  </si>
+  <si>
+    <t>Марьям</t>
+  </si>
+  <si>
+    <t>Дмитриевна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кочеткова  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Малышева  </t>
+  </si>
+  <si>
+    <t>Василиса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кузнецов  </t>
+  </si>
+  <si>
+    <t>Юрий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Александров  </t>
+  </si>
+  <si>
+    <t>Александрович</t>
+  </si>
+  <si>
+    <t>Ксения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Харитонова  </t>
+  </si>
+  <si>
+    <t>Егоровна</t>
+  </si>
+  <si>
+    <t>Марьяна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дроздова  </t>
+  </si>
+  <si>
+    <t>Степановна</t>
+  </si>
+  <si>
+    <t>Иванович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Быков  </t>
+  </si>
+  <si>
+    <t>Илья</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тарасов  </t>
+  </si>
+  <si>
+    <t>Артём</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Смирнова  </t>
+  </si>
+  <si>
+    <t>Вероника</t>
+  </si>
+  <si>
+    <t>Мироновна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корнилова  </t>
+  </si>
+  <si>
+    <t>Арина</t>
+  </si>
+  <si>
+    <t>Ивановна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Макарова  </t>
+  </si>
+  <si>
+    <t>Алиса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рубцова  </t>
+  </si>
+  <si>
+    <t>Александра</t>
+  </si>
+  <si>
+    <t>Семёновна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Соболева  </t>
+  </si>
+  <si>
+    <t>Ева</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Большаков  </t>
+  </si>
+  <si>
+    <t>Богдан</t>
+  </si>
+  <si>
+    <t>Владимировна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лаврентьева  </t>
+  </si>
+  <si>
+    <t>Ольга</t>
+  </si>
+  <si>
+    <t>Воробьева</t>
+  </si>
+  <si>
+    <t>Тихоновна</t>
+  </si>
+  <si>
+    <t>Захарова</t>
+  </si>
+  <si>
+    <t>Марковна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трофимова  </t>
+  </si>
+  <si>
+    <t>Софья</t>
   </si>
 </sst>
 </file>
@@ -792,375 +885,591 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>49</v>
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>30</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>56</v>
+        <v>32</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>60</v>
+        <v>36</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>63</v>
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>64</v>
+        <v>40</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>67</v>
+        <v>43</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>70</v>
+        <v>46</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>73</v>
+        <v>49</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>76</v>
+        <v>52</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>55</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="4" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="4" t="s">
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B30" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="4" t="s">
+      <c r="C30" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
+    <row r="32" spans="1:4">
+      <c r="A32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="B33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C34" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="4" t="s">
+    <row r="47" spans="1:3">
+      <c r="A47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="C48" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
+        <v>135</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="4" t="s">
-        <v>42</v>
+        <v>137</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/лаб.xlsx
+++ b/лаб.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="144">
   <si>
     <t>Имя</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Ж</t>
   </si>
   <si>
-    <t>Якубенко</t>
-  </si>
-  <si>
     <t>Роман</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t>М</t>
   </si>
   <si>
-    <t>13.15.2021</t>
-  </si>
-  <si>
     <t>Симонова</t>
   </si>
   <si>
@@ -105,9 +99,6 @@
     <t>Дмитрий</t>
   </si>
   <si>
-    <t xml:space="preserve">Захаров  </t>
-  </si>
-  <si>
     <t>Егорович</t>
   </si>
   <si>
@@ -123,12 +114,6 @@
     <t>Александр</t>
   </si>
   <si>
-    <t xml:space="preserve">Королев  </t>
-  </si>
-  <si>
-    <t>Григорьевич</t>
-  </si>
-  <si>
     <t>Иван</t>
   </si>
   <si>
@@ -171,9 +156,6 @@
     <t>Екатерина</t>
   </si>
   <si>
-    <t>Меркулова</t>
-  </si>
-  <si>
     <t>Матвеевна</t>
   </si>
   <si>
@@ -433,6 +415,39 @@
   </si>
   <si>
     <t>Софья</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Карпов</t>
+  </si>
+  <si>
+    <t>Пепел</t>
+  </si>
+  <si>
+    <t>Андреевич</t>
+  </si>
+  <si>
+    <t>ЯКУБОВИЧ</t>
+  </si>
+  <si>
+    <t>ЛОБЯН</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>tester</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>WEB dev</t>
+  </si>
+  <si>
+    <t>ee</t>
   </si>
 </sst>
 </file>
@@ -481,7 +496,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -494,6 +509,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -790,7 +809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="4" customWidth="1"/>
@@ -798,14 +817,15 @@
     <col min="3" max="3" width="16.42578125" style="4" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="4"/>
     <col min="5" max="5" width="15.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="3"/>
-    <col min="8" max="8" width="9.85546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" style="4" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" style="4" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="4"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -837,7 +857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -851,629 +871,1268 @@
         <v>13</v>
       </c>
       <c r="E2" s="1">
-        <v>26617</v>
-      </c>
-      <c r="F2" s="1" t="s">
+        <v>30722</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>38</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G50" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>32</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="3">
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="C17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2">
-        <v>22560</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="E17" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G24" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G26" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G27" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G28" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G29" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G32" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="C33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G33" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G35" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G36" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G37" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G38" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G39" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G40" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G41" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G43" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G44" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G45" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G46" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G47" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="C48" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G48" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G49" s="5">
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="4" t="s">
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G50" s="5">
+        <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="4" t="s">
+      <c r="H50" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>136</v>
+      <c r="I50" s="4" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 

--- a/лаб.xlsx
+++ b/лаб.xlsx
@@ -4,19 +4,22 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="19155" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="19155" windowHeight="11835" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="стандарт лист" sheetId="1" r:id="rId1"/>
+    <sheet name="сортировка фамилия" sheetId="2" r:id="rId2"/>
+    <sheet name="сортировка имени" sheetId="3" r:id="rId3"/>
+    <sheet name="сортировка отчество" sheetId="4" r:id="rId4"/>
+    <sheet name="сортировка дата рождения" sheetId="5" r:id="rId5"/>
+    <sheet name="Лист3" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="152">
   <si>
     <t>Имя</t>
   </si>
@@ -429,25 +432,49 @@
     <t>Андреевич</t>
   </si>
   <si>
-    <t>ЯКУБОВИЧ</t>
-  </si>
-  <si>
-    <t>ЛОБЯН</t>
-  </si>
-  <si>
-    <t>CEO</t>
-  </si>
-  <si>
-    <t>tester</t>
-  </si>
-  <si>
     <t>Data Science</t>
   </si>
   <si>
     <t>WEB dev</t>
   </si>
   <si>
-    <t>ee</t>
+    <t>Специалист по сетевому обеспечению</t>
+  </si>
+  <si>
+    <t>Системный аналитик</t>
+  </si>
+  <si>
+    <t>Программист</t>
+  </si>
+  <si>
+    <t>Системный администратор</t>
+  </si>
+  <si>
+    <t>Руководитель отдела информационных технологий</t>
+  </si>
+  <si>
+    <t>Маркетинг</t>
+  </si>
+  <si>
+    <t>SEO-специалист</t>
+  </si>
+  <si>
+    <t>Копирайтер</t>
+  </si>
+  <si>
+    <t>Продакт-менеджер</t>
+  </si>
+  <si>
+    <t>Клининг</t>
+  </si>
+  <si>
+    <t>Уборка</t>
+  </si>
+  <si>
+    <t>Куб</t>
+  </si>
+  <si>
+    <t>Лютик</t>
   </si>
 </sst>
 </file>
@@ -820,7 +847,7 @@
     <col min="6" max="6" width="20.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" style="3" customWidth="1"/>
     <col min="8" max="8" width="23.5703125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="48.7109375" style="4" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="4"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
   </cols>
@@ -884,12 +911,15 @@
         <v>133</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -911,7 +941,13 @@
         <v>32</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>143</v>
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20000</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -937,8 +973,14 @@
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="I4" s="4" t="s">
         <v>140</v>
+      </c>
+      <c r="J4" s="4">
+        <v>20000</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -964,6 +1006,15 @@
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
+      <c r="H5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="4">
+        <v>70034</v>
+      </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
@@ -992,12 +1043,15 @@
         <v>133</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
+      </c>
+      <c r="J6" s="4">
+        <v>70034</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>26</v>
@@ -1018,6 +1072,15 @@
         <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
+      <c r="H7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7" s="4">
+        <v>20000</v>
+      </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="4" t="s">
@@ -1042,6 +1105,15 @@
         <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
+      <c r="H8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="4">
+        <v>70034</v>
+      </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="4" t="s">
@@ -1066,6 +1138,15 @@
         <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
+      <c r="H9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="4">
+        <v>21310</v>
+      </c>
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11">
@@ -1095,7 +1176,10 @@
         <v>133</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
+      </c>
+      <c r="J10" s="4">
+        <v>70034</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1121,6 +1205,15 @@
         <f t="shared" ca="1" si="0"/>
         <v>46</v>
       </c>
+      <c r="H11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="4">
+        <v>70034</v>
+      </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="4" t="s">
@@ -1145,6 +1238,15 @@
         <f t="shared" ca="1" si="0"/>
         <v>33</v>
       </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" s="4">
+        <v>100000</v>
+      </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="4" t="s">
@@ -1169,10 +1271,19 @@
         <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
+      <c r="H13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="4">
+        <v>70034</v>
+      </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="4" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>45</v>
@@ -1193,6 +1304,15 @@
         <f t="shared" ca="1" si="0"/>
         <v>46</v>
       </c>
+      <c r="H14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="4">
+        <v>100000</v>
+      </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="4" t="s">
@@ -1221,7 +1341,10 @@
         <v>133</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="J15" s="4">
+        <v>31000</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1251,10 +1374,13 @@
         <v>133</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>137</v>
+      </c>
+      <c r="J16" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
         <v>53</v>
       </c>
@@ -1277,8 +1403,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="H17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J17" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
         <v>55</v>
       </c>
@@ -1301,8 +1436,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="H18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J18" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
         <v>58</v>
       </c>
@@ -1325,8 +1469,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -1353,10 +1506,13 @@
         <v>133</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>139</v>
+      </c>
+      <c r="J20" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
         <v>64</v>
       </c>
@@ -1379,8 +1535,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="H21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
         <v>67</v>
       </c>
@@ -1403,8 +1568,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="H22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J22" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
         <v>68</v>
       </c>
@@ -1427,8 +1601,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="H23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
         <v>71</v>
       </c>
@@ -1451,8 +1634,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="H24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
         <v>74</v>
       </c>
@@ -1479,10 +1671,13 @@
         <v>133</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>138</v>
+      </c>
+      <c r="J25" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
         <v>77</v>
       </c>
@@ -1505,8 +1700,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>44</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
         <v>78</v>
       </c>
@@ -1529,8 +1733,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="H27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
         <v>81</v>
       </c>
@@ -1553,8 +1766,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
         <v>83</v>
       </c>
@@ -1581,10 +1803,13 @@
         <v>133</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>139</v>
+      </c>
+      <c r="J29" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
         <v>85</v>
       </c>
@@ -1611,10 +1836,13 @@
         <v>133</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>138</v>
+      </c>
+      <c r="J30" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
         <v>88</v>
       </c>
@@ -1641,10 +1869,13 @@
         <v>133</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>142</v>
+      </c>
+      <c r="J31" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
         <v>47</v>
       </c>
@@ -1667,8 +1898,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="H32" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J32" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
         <v>91</v>
       </c>
@@ -1691,8 +1931,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="H33" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J33" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
         <v>92</v>
       </c>
@@ -1719,10 +1968,13 @@
         <v>133</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>138</v>
+      </c>
+      <c r="J34" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
         <v>94</v>
       </c>
@@ -1745,8 +1997,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="H35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J35" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
         <v>96</v>
       </c>
@@ -1769,8 +2030,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>44</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="H36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J36" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
         <v>99</v>
       </c>
@@ -1797,10 +2067,13 @@
         <v>133</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>138</v>
+      </c>
+      <c r="J37" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
         <v>102</v>
       </c>
@@ -1823,8 +2096,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="H38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J38" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
         <v>105</v>
       </c>
@@ -1847,8 +2129,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="H39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J39" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
         <v>107</v>
       </c>
@@ -1871,8 +2162,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="H40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J40" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
         <v>109</v>
       </c>
@@ -1899,10 +2199,13 @@
         <v>133</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>137</v>
+      </c>
+      <c r="J41" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
         <v>112</v>
       </c>
@@ -1925,8 +2228,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="H42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J42" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
         <v>115</v>
       </c>
@@ -1949,8 +2261,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="H43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J43" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
         <v>117</v>
       </c>
@@ -1973,8 +2294,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="H44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J44" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
         <v>120</v>
       </c>
@@ -2001,10 +2331,13 @@
         <v>133</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>137</v>
+      </c>
+      <c r="J45" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
         <v>122</v>
       </c>
@@ -2027,8 +2360,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="H46" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J46" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
         <v>125</v>
       </c>
@@ -2051,8 +2393,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="H47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J47" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
         <v>127</v>
       </c>
@@ -2075,8 +2426,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="H48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J48" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
         <v>129</v>
       </c>
@@ -2099,8 +2459,17 @@
         <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="50" spans="1:9">
+      <c r="H49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J49" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
         <v>131</v>
       </c>
@@ -2127,10 +2496,18 @@
         <v>133</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="J50" s="4">
+        <v>21310</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
@@ -2138,18 +2515,8384 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="38.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>32</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G3" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>44</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G4" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <v>38</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J4" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G5" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <v>38</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G6" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <v>41</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J6" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G7" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <v>33</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G8" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <v>47</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J8" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G9" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <v>34</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J9" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G10" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <v>45</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J10" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G11" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <v>40</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J11" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G12" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <v>39</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J12" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G13" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <v>38</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G14" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <v>36</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J14" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G15" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <v>45</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J15" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G16" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <v>34</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J16" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G17" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <v>30</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G18" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <v>40</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J18" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G19" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <v>38</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G20" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <v>32</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J20" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G21" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <v>42</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J21" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G22" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <v>34</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J22" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G23" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <v>32</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G24" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <v>32</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J24" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G25" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <v>37</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J25" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G26" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <v>41</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J26" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G27" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <v>43</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J27" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G28" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <v>46</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G29" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <v>30</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J29" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G30" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <v>45</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J30" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G31" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <v>35</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G32" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <v>30</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J32" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G33" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <v>46</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J33" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G34" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <v>43</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J34" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G35" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <v>36</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J35" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G36" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <v>36</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J36" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G37" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <v>45</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J37" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G38" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <v>47</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J38" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G39" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <v>42</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J39" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G40" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <v>43</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J40" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G41" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <v>44</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J41" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G42" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <v>41</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J42" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G43" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <v>37</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J43" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G44" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <v>40</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J44" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G45" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <v>42</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J45" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G46" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <v>35</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J46" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G47" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <v>30</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J47" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G48" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <v>45</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J48" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G49" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <v>32</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J49" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G50" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <v>43</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J50" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:J50">
+    <sortCondition ref="A1"/>
+  </sortState>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" customWidth="1"/>
+    <col min="9" max="9" width="41.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>38</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G3" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>41</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G4" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <v>43</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G5" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <v>36</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G6" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <v>33</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G7" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <v>30</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J7" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G8" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <v>45</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J8" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G9" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <v>32</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G10" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <v>30</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J10" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G11" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <v>43</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G12" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <v>34</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J12" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G13" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <v>42</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G14" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <v>45</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J14" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G15" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <v>41</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J15" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G16" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <v>45</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J16" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G17" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <v>42</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G18" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <v>47</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J18" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G19" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <v>45</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G20" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <v>45</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G21" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <v>38</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J21" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G22" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <v>43</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J22" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G23" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <v>36</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J23" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G24" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <v>32</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G25" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <v>37</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J25" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G26" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <v>47</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J26" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G27" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <v>34</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G28" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <v>46</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G29" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <v>35</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J29" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G30" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <v>41</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J30" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G31" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <v>38</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J31" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G32" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <v>34</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J32" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G33" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <v>32</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J33" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G34" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <v>30</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J34" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G35" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <v>35</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J35" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G36" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <v>39</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J36" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G37" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <v>36</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J37" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G38" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <v>43</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J38" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G39" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <v>40</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J39" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G40" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <v>30</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J40" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G41" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <v>40</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J41" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G42" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <v>32</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J42" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G43" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <v>38</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J43" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G44" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <v>32</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J44" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G45" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <v>40</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J45" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G46" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <v>44</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J46" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G47" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <v>37</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J47" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G48" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <v>46</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J48" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G49" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <v>42</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J49" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G50" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <v>44</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J50" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:J50">
+    <sortCondition ref="B1"/>
+  </sortState>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="9" max="9" width="33.85546875" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>38</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G3" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>44</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G4" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <v>40</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G5" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <v>44</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J5" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G6" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <v>43</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J6" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G7" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <v>41</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J7" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G8" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <v>41</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J8" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G9" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <v>42</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G10" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <v>43</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J10" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G11" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <v>45</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G12" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <v>38</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J12" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G13" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <v>41</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G14" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <v>43</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G15" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <v>43</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J15" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G16" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <v>45</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J16" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G17" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <v>30</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J17" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G18" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <v>38</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J18" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G19" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <v>32</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J19" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G20" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <v>40</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J20" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G21" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <v>37</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J21" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G22" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <v>30</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J22" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G23" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <v>34</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J23" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G24" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <v>30</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J24" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G25" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <v>45</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G26" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <v>42</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J26" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G27" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <v>32</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G28" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <v>30</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G29" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <v>32</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J29" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G30" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <v>36</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J30" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G31" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <v>38</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J31" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G32" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <v>36</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J32" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G33" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <v>42</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J33" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G34" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <v>45</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J34" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G35" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <v>45</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J35" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G36" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <v>37</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J36" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G37" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <v>32</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J37" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G38" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <v>34</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J38" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G39" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <v>35</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J39" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G40" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <v>47</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J40" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G41" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <v>40</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J41" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G42" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <v>35</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J42" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G43" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <v>32</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J43" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G44" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <v>33</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J44" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G45" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <v>47</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J45" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G46" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <v>39</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J46" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G47" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <v>46</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J47" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G48" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <v>36</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J48" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G49" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <v>34</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J49" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G50" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <v>46</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J50" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:J50">
+    <sortCondition ref="C1"/>
+  </sortState>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>47</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G3" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>47</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G4" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <v>46</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J4" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G5" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <v>46</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J5" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G6" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <v>45</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J6" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G7" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <v>45</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J7" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G8" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <v>45</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J8" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G9" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <v>45</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G10" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <v>45</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J10" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G11" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <v>44</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J11" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G12" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <v>44</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J12" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G13" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <v>43</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J13" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G14" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <v>43</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G15" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <v>43</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J15" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G16" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G17" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <v>42</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G18" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <v>42</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G19" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <v>42</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G20" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <v>41</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J20" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G21" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <v>41</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J21" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G22" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <v>41</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J22" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G23" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <v>40</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G24" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <v>40</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G25" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <v>40</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J25" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G26" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <v>39</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G27" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <v>38</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G28" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <v>38</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G29" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <v>38</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J29" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G30" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <v>38</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J30" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G31" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <v>37</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J31" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G32" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <v>37</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J32" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G33" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <v>36</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J33" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G34" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <v>36</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J34" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G35" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <v>36</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J35" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G36" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <v>35</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J36" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G37" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <v>35</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J37" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G38" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <v>34</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J38" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G39" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <v>34</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J39" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G40" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <v>34</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J40" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G41" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <v>33</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J41" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G42" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <v>32</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J42" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G43" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <v>32</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J43" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G44" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <v>32</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J44" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G45" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <v>32</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J45" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G46" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <v>32</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J46" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G47" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <v>30</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J47" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G48" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <v>30</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J48" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G49" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <v>30</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J49" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G50" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <v>30</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J50" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:J50">
+    <sortCondition ref="E1"/>
+  </sortState>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="10" width="25.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>38</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G50" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>32</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J6" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J15" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J17" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J18" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J20" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J22" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G24" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J25" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G26" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G27" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G28" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G29" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J29" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J30" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G32" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J32" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G33" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J33" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J34" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G35" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J35" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G36" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J36" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G37" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J37" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G38" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J38" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G39" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J39" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G40" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J40" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G41" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J41" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J42" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G43" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J43" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G44" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J44" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G45" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J45" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G46" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J46" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G47" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J47" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G48" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J48" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G49" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J49" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G50" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J50" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/лаб.xlsx
+++ b/лаб.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="19155" windowHeight="11835" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="19155" windowHeight="11835" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="стандарт лист" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,18 @@
     <sheet name="сортировка имени" sheetId="3" r:id="rId3"/>
     <sheet name="сортировка отчество" sheetId="4" r:id="rId4"/>
     <sheet name="сортировка дата рождения" sheetId="5" r:id="rId5"/>
-    <sheet name="Лист3" sheetId="6" r:id="rId6"/>
+    <sheet name="особая сортировка по отделу" sheetId="6" r:id="rId6"/>
+    <sheet name="Авто фильтр" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Авто фильтр'!$A$1:$J$50</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="155">
   <si>
     <t>Имя</t>
   </si>
@@ -475,6 +479,15 @@
   </si>
   <si>
     <t>Лютик</t>
+  </si>
+  <si>
+    <t>Кожан</t>
+  </si>
+  <si>
+    <t>Виктория</t>
+  </si>
+  <si>
+    <t>Даниилова</t>
   </si>
 </sst>
 </file>
@@ -2580,7 +2593,7 @@
         <v>44504</v>
       </c>
       <c r="G2" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <f t="shared" ref="G2:G33" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
         <v>32</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -2613,7 +2626,7 @@
         <v>44516</v>
       </c>
       <c r="G3" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>44</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -2646,7 +2659,7 @@
         <v>44482</v>
       </c>
       <c r="G4" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -2679,7 +2692,7 @@
         <v>44499</v>
       </c>
       <c r="G5" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -2712,7 +2725,7 @@
         <v>44526</v>
       </c>
       <c r="G6" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -2745,7 +2758,7 @@
         <v>44492</v>
       </c>
       <c r="G7" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>33</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -2778,7 +2791,7 @@
         <v>44503</v>
       </c>
       <c r="G8" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>47</v>
       </c>
       <c r="H8" s="4" t="s">
@@ -2811,7 +2824,7 @@
         <v>44519</v>
       </c>
       <c r="G9" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -2844,7 +2857,7 @@
         <v>44509</v>
       </c>
       <c r="G10" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -2877,7 +2890,7 @@
         <v>44528</v>
       </c>
       <c r="G11" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -2910,7 +2923,7 @@
         <v>44518</v>
       </c>
       <c r="G12" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>39</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -2943,7 +2956,7 @@
         <v>44497</v>
       </c>
       <c r="G13" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -2976,7 +2989,7 @@
         <v>44485</v>
       </c>
       <c r="G14" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -3009,7 +3022,7 @@
         <v>44507</v>
       </c>
       <c r="G15" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -3042,7 +3055,7 @@
         <v>44529</v>
       </c>
       <c r="G16" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -3075,7 +3088,7 @@
         <v>44486</v>
       </c>
       <c r="G17" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -3108,7 +3121,7 @@
         <v>44489</v>
       </c>
       <c r="G18" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -3141,7 +3154,7 @@
         <v>44508</v>
       </c>
       <c r="G19" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -3174,7 +3187,7 @@
         <v>44495</v>
       </c>
       <c r="G20" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -3207,7 +3220,7 @@
         <v>44512</v>
       </c>
       <c r="G21" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -3240,7 +3253,7 @@
         <v>44522</v>
       </c>
       <c r="G22" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -3273,7 +3286,7 @@
         <v>44513</v>
       </c>
       <c r="G23" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -3306,7 +3319,7 @@
         <v>44483</v>
       </c>
       <c r="G24" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -3339,7 +3352,7 @@
         <v>44487</v>
       </c>
       <c r="G25" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -3372,7 +3385,7 @@
         <v>44515</v>
       </c>
       <c r="G26" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H26" s="4" t="s">
@@ -3405,7 +3418,7 @@
         <v>44527</v>
       </c>
       <c r="G27" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -3438,7 +3451,7 @@
         <v>44494</v>
       </c>
       <c r="G28" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>46</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -3471,7 +3484,7 @@
         <v>44523</v>
       </c>
       <c r="G29" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -3504,7 +3517,7 @@
         <v>44514</v>
       </c>
       <c r="G30" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -3537,7 +3550,7 @@
         <v>44511</v>
       </c>
       <c r="G31" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>35</v>
       </c>
       <c r="H31" s="4" t="s">
@@ -3570,7 +3583,7 @@
         <v>44488</v>
       </c>
       <c r="G32" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H32" s="4" t="s">
@@ -3603,7 +3616,7 @@
         <v>44491</v>
       </c>
       <c r="G33" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>46</v>
       </c>
       <c r="H33" s="4" t="s">
@@ -3636,7 +3649,7 @@
         <v>44524</v>
       </c>
       <c r="G34" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <f t="shared" ref="G34:G50" ca="1" si="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
         <v>43</v>
       </c>
       <c r="H34" s="4" t="s">
@@ -3669,7 +3682,7 @@
         <v>44484</v>
       </c>
       <c r="G35" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>36</v>
       </c>
       <c r="H35" s="4" t="s">
@@ -3702,7 +3715,7 @@
         <v>44498</v>
       </c>
       <c r="G36" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>36</v>
       </c>
       <c r="H36" s="4" t="s">
@@ -3735,7 +3748,7 @@
         <v>44521</v>
       </c>
       <c r="G37" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>45</v>
       </c>
       <c r="H37" s="4" t="s">
@@ -3768,7 +3781,7 @@
         <v>44525</v>
       </c>
       <c r="G38" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>47</v>
       </c>
       <c r="H38" s="4" t="s">
@@ -3801,7 +3814,7 @@
         <v>44520</v>
       </c>
       <c r="G39" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>42</v>
       </c>
       <c r="H39" s="4" t="s">
@@ -3834,7 +3847,7 @@
         <v>44496</v>
       </c>
       <c r="G40" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>43</v>
       </c>
       <c r="H40" s="4" t="s">
@@ -3867,7 +3880,7 @@
         <v>44506</v>
       </c>
       <c r="G41" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>44</v>
       </c>
       <c r="H41" s="4" t="s">
@@ -3900,7 +3913,7 @@
         <v>44502</v>
       </c>
       <c r="G42" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
       <c r="H42" s="4" t="s">
@@ -3933,7 +3946,7 @@
         <v>44530</v>
       </c>
       <c r="G43" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>37</v>
       </c>
       <c r="H43" s="4" t="s">
@@ -3966,7 +3979,7 @@
         <v>44501</v>
       </c>
       <c r="G44" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>40</v>
       </c>
       <c r="H44" s="4" t="s">
@@ -3999,7 +4012,7 @@
         <v>44505</v>
       </c>
       <c r="G45" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>42</v>
       </c>
       <c r="H45" s="4" t="s">
@@ -4032,7 +4045,7 @@
         <v>44490</v>
       </c>
       <c r="G46" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="H46" s="4" t="s">
@@ -4065,7 +4078,7 @@
         <v>44517</v>
       </c>
       <c r="G47" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>30</v>
       </c>
       <c r="H47" s="4" t="s">
@@ -4098,7 +4111,7 @@
         <v>44500</v>
       </c>
       <c r="G48" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>45</v>
       </c>
       <c r="H48" s="4" t="s">
@@ -4131,7 +4144,7 @@
         <v>44510</v>
       </c>
       <c r="G49" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H49" s="4" t="s">
@@ -4164,7 +4177,7 @@
         <v>44493</v>
       </c>
       <c r="G50" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>43</v>
       </c>
       <c r="H50" s="4" t="s">
@@ -4239,296 +4252,296 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1">
-        <v>30722</v>
+        <v>29857</v>
       </c>
       <c r="F2" s="1">
-        <v>44482</v>
+        <v>44515</v>
       </c>
       <c r="G2" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J2" s="4">
-        <v>20000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1">
-        <v>29857</v>
+        <v>29038</v>
       </c>
       <c r="F3" s="1">
-        <v>44515</v>
+        <v>44524</v>
       </c>
       <c r="G3" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J3" s="4">
-        <v>31000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="1">
-        <v>29038</v>
+        <v>31434</v>
       </c>
       <c r="F4" s="1">
-        <v>44524</v>
+        <v>44485</v>
       </c>
       <c r="G4" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J4" s="4">
-        <v>100000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="1">
-        <v>31434</v>
+        <v>32646</v>
       </c>
       <c r="F5" s="1">
-        <v>44485</v>
+        <v>44492</v>
       </c>
       <c r="G5" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="J5" s="4">
-        <v>70034</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="1">
-        <v>32646</v>
+        <v>33771</v>
       </c>
       <c r="F6" s="1">
-        <v>44492</v>
+        <v>44523</v>
       </c>
       <c r="G6" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J6" s="4">
-        <v>100000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="1">
-        <v>33771</v>
+        <v>28136</v>
       </c>
       <c r="F7" s="1">
-        <v>44523</v>
+        <v>44507</v>
       </c>
       <c r="G7" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J7" s="4">
-        <v>70034</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="1">
-        <v>28136</v>
+        <v>33082</v>
       </c>
       <c r="F8" s="1">
-        <v>44507</v>
+        <v>44495</v>
       </c>
       <c r="G8" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="J8" s="4">
-        <v>40000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1">
-        <v>33082</v>
+        <v>33856</v>
       </c>
       <c r="F9" s="1">
-        <v>44495</v>
+        <v>44488</v>
       </c>
       <c r="G9" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J9" s="4">
-        <v>31000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>33856</v>
+        <v>29013</v>
       </c>
       <c r="F10" s="1">
-        <v>44488</v>
+        <v>44493</v>
       </c>
       <c r="G10" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J10" s="4">
         <v>70034</v>
@@ -4536,125 +4549,125 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="1">
-        <v>29013</v>
+        <v>32297</v>
       </c>
       <c r="F11" s="1">
-        <v>44493</v>
+        <v>44522</v>
       </c>
       <c r="G11" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J11" s="4">
-        <v>70034</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E12" s="1">
-        <v>32297</v>
+        <v>29547</v>
       </c>
       <c r="F12" s="1">
-        <v>44522</v>
+        <v>44520</v>
       </c>
       <c r="G12" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J12" s="4">
-        <v>80000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="1">
-        <v>29547</v>
+        <v>28388</v>
       </c>
       <c r="F13" s="1">
-        <v>44520</v>
+        <v>44509</v>
       </c>
       <c r="G13" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J13" s="4">
-        <v>100000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="1">
-        <v>28388</v>
+        <v>29808</v>
       </c>
       <c r="F14" s="1">
-        <v>44509</v>
+        <v>44526</v>
       </c>
       <c r="G14" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>133</v>
@@ -4663,31 +4676,31 @@
         <v>139</v>
       </c>
       <c r="J14" s="4">
-        <v>20000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1">
-        <v>29808</v>
+        <v>28208</v>
       </c>
       <c r="F15" s="1">
-        <v>44526</v>
+        <v>44500</v>
       </c>
       <c r="G15" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>133</v>
@@ -4696,114 +4709,114 @@
         <v>139</v>
       </c>
       <c r="J15" s="4">
-        <v>100000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="1">
-        <v>28208</v>
+        <v>29561</v>
       </c>
       <c r="F16" s="1">
-        <v>44500</v>
+        <v>44512</v>
       </c>
       <c r="G16" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J16" s="4">
-        <v>31000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1">
-        <v>29561</v>
+        <v>27489</v>
       </c>
       <c r="F17" s="1">
-        <v>44512</v>
+        <v>44503</v>
       </c>
       <c r="G17" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J17" s="4">
-        <v>100000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1">
-        <v>27489</v>
+        <v>28186</v>
       </c>
       <c r="F18" s="1">
-        <v>44503</v>
+        <v>44514</v>
       </c>
       <c r="G18" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J18" s="4">
-        <v>20000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>20</v>
@@ -4812,10 +4825,10 @@
         <v>13</v>
       </c>
       <c r="E19" s="1">
-        <v>28186</v>
+        <v>28277</v>
       </c>
       <c r="F19" s="1">
-        <v>44514</v>
+        <v>44521</v>
       </c>
       <c r="G19" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
@@ -4825,43 +4838,43 @@
         <v>133</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J19" s="4">
-        <v>31000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="1">
-        <v>28277</v>
+        <v>30722</v>
       </c>
       <c r="F20" s="1">
-        <v>44521</v>
+        <v>44482</v>
       </c>
       <c r="G20" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J20" s="4">
-        <v>80000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5916,32 +5929,32 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1">
-        <v>30722</v>
+        <v>28780</v>
       </c>
       <c r="F2" s="1">
-        <v>44482</v>
+        <v>44516</v>
       </c>
       <c r="G2" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J2" s="4">
         <v>20000</v>
@@ -5949,76 +5962,76 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="1">
-        <v>28780</v>
+        <v>30198</v>
       </c>
       <c r="F3" s="1">
-        <v>44516</v>
+        <v>44489</v>
       </c>
       <c r="G3" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J3" s="4">
-        <v>20000</v>
+        <v>21310</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1">
-        <v>30198</v>
+        <v>28784</v>
       </c>
       <c r="F4" s="1">
-        <v>44489</v>
+        <v>44506</v>
       </c>
       <c r="G4" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J4" s="4">
-        <v>21310</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>76</v>
@@ -6027,20 +6040,20 @@
         <v>13</v>
       </c>
       <c r="E5" s="1">
-        <v>28784</v>
+        <v>29038</v>
       </c>
       <c r="F5" s="1">
-        <v>44506</v>
+        <v>44524</v>
       </c>
       <c r="G5" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J5" s="4">
         <v>100000</v>
@@ -6048,43 +6061,43 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1">
-        <v>29038</v>
+        <v>29640</v>
       </c>
       <c r="F6" s="1">
-        <v>44524</v>
+        <v>44502</v>
       </c>
       <c r="G6" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J6" s="4">
-        <v>100000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>66</v>
@@ -6093,31 +6106,31 @@
         <v>16</v>
       </c>
       <c r="E7" s="1">
-        <v>29640</v>
+        <v>29857</v>
       </c>
       <c r="F7" s="1">
-        <v>44502</v>
+        <v>44515</v>
       </c>
       <c r="G7" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
         <v>41</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="J7" s="4">
-        <v>20000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>66</v>
@@ -6126,64 +6139,64 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <v>29857</v>
+        <v>29547</v>
       </c>
       <c r="F8" s="1">
-        <v>44515</v>
+        <v>44520</v>
       </c>
       <c r="G8" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J8" s="4">
-        <v>31000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1">
-        <v>29547</v>
+        <v>29013</v>
       </c>
       <c r="F9" s="1">
-        <v>44520</v>
+        <v>44493</v>
       </c>
       <c r="G9" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J9" s="4">
-        <v>100000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>41</v>
@@ -6192,14 +6205,14 @@
         <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>29013</v>
+        <v>28136</v>
       </c>
       <c r="F10" s="1">
-        <v>44493</v>
+        <v>44507</v>
       </c>
       <c r="G10" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>148</v>
@@ -6208,48 +6221,48 @@
         <v>149</v>
       </c>
       <c r="J10" s="4">
-        <v>70034</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E11" s="1">
-        <v>28136</v>
+        <v>30716</v>
       </c>
       <c r="F11" s="1">
-        <v>44507</v>
+        <v>44499</v>
       </c>
       <c r="G11" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J11" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>57</v>
@@ -6258,76 +6271,76 @@
         <v>16</v>
       </c>
       <c r="E12" s="1">
-        <v>30716</v>
+        <v>29808</v>
       </c>
       <c r="F12" s="1">
-        <v>44499</v>
+        <v>44526</v>
       </c>
       <c r="G12" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J12" s="4">
-        <v>20000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1">
-        <v>29808</v>
+        <v>29109</v>
       </c>
       <c r="F13" s="1">
-        <v>44526</v>
+        <v>44527</v>
       </c>
       <c r="G13" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J13" s="4">
-        <v>100000</v>
+        <v>211000</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="1">
-        <v>29109</v>
+        <v>28967</v>
       </c>
       <c r="F14" s="1">
-        <v>44527</v>
+        <v>44496</v>
       </c>
       <c r="G14" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
@@ -6340,40 +6353,40 @@
         <v>137</v>
       </c>
       <c r="J14" s="4">
-        <v>211000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="1">
-        <v>28967</v>
+        <v>30722</v>
       </c>
       <c r="F15" s="1">
-        <v>44496</v>
+        <v>44482</v>
       </c>
       <c r="G15" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J15" s="4">
-        <v>100000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7612,7 +7625,7 @@
         <v>44503</v>
       </c>
       <c r="G2" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <f t="shared" ref="G2:G33" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
         <v>47</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -7645,7 +7658,7 @@
         <v>44525</v>
       </c>
       <c r="G3" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>47</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -7678,7 +7691,7 @@
         <v>44494</v>
       </c>
       <c r="G4" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>46</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -7711,7 +7724,7 @@
         <v>44491</v>
       </c>
       <c r="G5" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>46</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -7744,7 +7757,7 @@
         <v>44507</v>
       </c>
       <c r="G6" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -7777,7 +7790,7 @@
         <v>44514</v>
       </c>
       <c r="G7" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -7810,7 +7823,7 @@
         <v>44500</v>
       </c>
       <c r="G8" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H8" s="4" t="s">
@@ -7843,7 +7856,7 @@
         <v>44521</v>
       </c>
       <c r="G9" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -7876,7 +7889,7 @@
         <v>44509</v>
       </c>
       <c r="G10" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -7909,7 +7922,7 @@
         <v>44516</v>
       </c>
       <c r="G11" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>44</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -7942,7 +7955,7 @@
         <v>44506</v>
       </c>
       <c r="G12" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>44</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -7975,7 +7988,7 @@
         <v>44496</v>
       </c>
       <c r="G13" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -8008,7 +8021,7 @@
         <v>44493</v>
       </c>
       <c r="G14" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -8041,7 +8054,7 @@
         <v>44524</v>
       </c>
       <c r="G15" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -8074,7 +8087,7 @@
         <v>44527</v>
       </c>
       <c r="G16" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -8107,7 +8120,7 @@
         <v>44520</v>
       </c>
       <c r="G17" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -8140,7 +8153,7 @@
         <v>44512</v>
       </c>
       <c r="G18" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -8173,7 +8186,7 @@
         <v>44505</v>
       </c>
       <c r="G19" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -8206,7 +8219,7 @@
         <v>44502</v>
       </c>
       <c r="G20" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -8239,7 +8252,7 @@
         <v>44526</v>
       </c>
       <c r="G21" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -8272,7 +8285,7 @@
         <v>44515</v>
       </c>
       <c r="G22" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -8305,7 +8318,7 @@
         <v>44528</v>
       </c>
       <c r="G23" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -8338,7 +8351,7 @@
         <v>44501</v>
       </c>
       <c r="G24" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -8371,7 +8384,7 @@
         <v>44489</v>
       </c>
       <c r="G25" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -8404,7 +8417,7 @@
         <v>44518</v>
       </c>
       <c r="G26" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>39</v>
       </c>
       <c r="H26" s="4" t="s">
@@ -8437,7 +8450,7 @@
         <v>44508</v>
       </c>
       <c r="G27" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -8470,7 +8483,7 @@
         <v>44499</v>
       </c>
       <c r="G28" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -8503,7 +8516,7 @@
         <v>44482</v>
       </c>
       <c r="G29" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -8536,7 +8549,7 @@
         <v>44497</v>
       </c>
       <c r="G30" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -8569,7 +8582,7 @@
         <v>44530</v>
       </c>
       <c r="G31" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
       <c r="H31" s="4" t="s">
@@ -8602,7 +8615,7 @@
         <v>44487</v>
       </c>
       <c r="G32" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
       <c r="H32" s="4" t="s">
@@ -8635,7 +8648,7 @@
         <v>44485</v>
       </c>
       <c r="G33" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H33" s="4" t="s">
@@ -8668,7 +8681,7 @@
         <v>44484</v>
       </c>
       <c r="G34" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <f t="shared" ref="G34:G50" ca="1" si="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
         <v>36</v>
       </c>
       <c r="H34" s="4" t="s">
@@ -8701,7 +8714,7 @@
         <v>44498</v>
       </c>
       <c r="G35" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>36</v>
       </c>
       <c r="H35" s="4" t="s">
@@ -8734,7 +8747,7 @@
         <v>44490</v>
       </c>
       <c r="G36" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="H36" s="4" t="s">
@@ -8767,7 +8780,7 @@
         <v>44511</v>
       </c>
       <c r="G37" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="H37" s="4" t="s">
@@ -8800,7 +8813,7 @@
         <v>44529</v>
       </c>
       <c r="G38" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>34</v>
       </c>
       <c r="H38" s="4" t="s">
@@ -8833,7 +8846,7 @@
         <v>44522</v>
       </c>
       <c r="G39" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>34</v>
       </c>
       <c r="H39" s="4" t="s">
@@ -8866,7 +8879,7 @@
         <v>44519</v>
       </c>
       <c r="G40" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>34</v>
       </c>
       <c r="H40" s="4" t="s">
@@ -8899,7 +8912,7 @@
         <v>44492</v>
       </c>
       <c r="G41" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>33</v>
       </c>
       <c r="H41" s="4" t="s">
@@ -8932,7 +8945,7 @@
         <v>44504</v>
       </c>
       <c r="G42" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H42" s="4" t="s">
@@ -8965,7 +8978,7 @@
         <v>44483</v>
       </c>
       <c r="G43" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H43" s="4" t="s">
@@ -8998,7 +9011,7 @@
         <v>44495</v>
       </c>
       <c r="G44" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H44" s="4" t="s">
@@ -9031,7 +9044,7 @@
         <v>44510</v>
       </c>
       <c r="G45" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H45" s="4" t="s">
@@ -9064,7 +9077,7 @@
         <v>44513</v>
       </c>
       <c r="G46" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H46" s="4" t="s">
@@ -9097,7 +9110,7 @@
         <v>44517</v>
       </c>
       <c r="G47" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>30</v>
       </c>
       <c r="H47" s="4" t="s">
@@ -9130,7 +9143,7 @@
         <v>44523</v>
       </c>
       <c r="G48" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>30</v>
       </c>
       <c r="H48" s="4" t="s">
@@ -9163,7 +9176,7 @@
         <v>44486</v>
       </c>
       <c r="G49" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>30</v>
       </c>
       <c r="H49" s="4" t="s">
@@ -9196,7 +9209,7 @@
         <v>44488</v>
       </c>
       <c r="G50" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>30</v>
       </c>
       <c r="H50" s="4" t="s">
@@ -9272,98 +9285,98 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1">
-        <v>30722</v>
+        <v>28013</v>
       </c>
       <c r="F2" s="1">
-        <v>44482</v>
+        <v>44491</v>
       </c>
       <c r="G2" s="5">
         <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="J2" s="4">
-        <v>20000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2">
-        <v>33057</v>
+        <v>13</v>
+      </c>
+      <c r="E3" s="1">
+        <v>29013</v>
       </c>
       <c r="F3" s="1">
-        <v>44483</v>
+        <v>44493</v>
       </c>
       <c r="G3" s="5">
-        <f t="shared" ref="G3:G50" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
-        <v>32</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>43</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="J3" s="4">
-        <v>20000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1">
-        <v>31518</v>
+        <v>32912</v>
       </c>
       <c r="F4" s="1">
-        <v>44484</v>
+        <v>44504</v>
       </c>
       <c r="G4" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="J4" s="4">
         <v>20000</v>
@@ -9371,65 +9384,65 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="1">
-        <v>31434</v>
+        <v>28136</v>
       </c>
       <c r="F5" s="1">
-        <v>44485</v>
+        <v>44507</v>
       </c>
       <c r="G5" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <v>45</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J5" s="4">
-        <v>70034</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1">
-        <v>33806</v>
+        <v>32382</v>
       </c>
       <c r="F6" s="1">
-        <v>44486</v>
+        <v>44519</v>
       </c>
       <c r="G6" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <v>34</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="J6" s="4">
         <v>70034</v>
@@ -9437,65 +9450,65 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1">
-        <v>31216</v>
+        <v>32293</v>
       </c>
       <c r="F7" s="1">
-        <v>44487</v>
+        <v>44529</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <v>34</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J7" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1">
-        <v>33856</v>
+        <v>31434</v>
       </c>
       <c r="F8" s="1">
-        <v>44488</v>
+        <v>44485</v>
       </c>
       <c r="G8" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <v>36</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>144</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J8" s="4">
         <v>70034</v>
@@ -9503,65 +9516,65 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="1">
-        <v>30198</v>
+        <v>31216</v>
       </c>
       <c r="F9" s="1">
-        <v>44489</v>
+        <v>44487</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <v>37</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J9" s="4">
-        <v>21310</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="1">
-        <v>31887</v>
+        <v>33856</v>
       </c>
       <c r="F10" s="1">
-        <v>44490</v>
+        <v>44488</v>
       </c>
       <c r="G10" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="J10" s="4">
         <v>70034</v>
@@ -9569,263 +9582,263 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G11" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
         <v>36</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="1">
-        <v>28013</v>
-      </c>
-      <c r="F11" s="1">
-        <v>44491</v>
-      </c>
-      <c r="G11" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>46</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J11" s="4">
-        <v>70034</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G12" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
         <v>40</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="1">
-        <v>32646</v>
-      </c>
-      <c r="F12" s="1">
-        <v>44492</v>
-      </c>
-      <c r="G12" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>33</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J12" s="4">
-        <v>100000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G13" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
         <v>41</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="1">
-        <v>29013</v>
-      </c>
-      <c r="F13" s="1">
-        <v>44493</v>
-      </c>
-      <c r="G13" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>43</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J13" s="4">
-        <v>70034</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E14" s="1">
-        <v>27847</v>
+        <v>27489</v>
       </c>
       <c r="F14" s="1">
-        <v>44494</v>
+        <v>44503</v>
       </c>
       <c r="G14" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <v>47</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J14" s="4">
-        <v>100000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="1">
-        <v>33082</v>
+        <v>33214</v>
       </c>
       <c r="F15" s="1">
-        <v>44495</v>
+        <v>44513</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
         <v>32</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J15" s="4">
-        <v>31000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="1">
-        <v>28967</v>
+        <v>33771</v>
       </c>
       <c r="F16" s="1">
-        <v>44496</v>
+        <v>44523</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <v>30</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J16" s="4">
-        <v>100000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E17" s="1">
-        <v>30813</v>
+        <v>30009</v>
       </c>
       <c r="F17" s="1">
-        <v>44497</v>
+        <v>44528</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <v>40</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J17" s="4">
-        <v>20000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="1">
-        <v>31684</v>
+        <v>30722</v>
       </c>
       <c r="F18" s="1">
-        <v>44498</v>
+        <v>44482</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <v>38</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J18" s="4">
         <v>20000</v>
@@ -9833,32 +9846,32 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="1">
-        <v>30716</v>
+      <c r="E19" s="2">
+        <v>33057</v>
       </c>
       <c r="F19" s="1">
-        <v>44499</v>
+        <v>44483</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <v>32</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J19" s="4">
         <v>20000</v>
@@ -9866,109 +9879,109 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="1">
-        <v>28208</v>
+        <v>31518</v>
       </c>
       <c r="F20" s="1">
-        <v>44500</v>
+        <v>44484</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <v>36</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J20" s="4">
-        <v>31000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="1">
-        <v>30065</v>
+        <v>33806</v>
       </c>
       <c r="F21" s="1">
-        <v>44501</v>
+        <v>44486</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <v>30</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="J21" s="4">
-        <v>31000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="1">
-        <v>29640</v>
+        <v>30198</v>
       </c>
       <c r="F22" s="1">
-        <v>44502</v>
+        <v>44489</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <v>40</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="J22" s="4">
-        <v>20000</v>
+        <v>21310</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>34</v>
@@ -9977,218 +9990,218 @@
         <v>16</v>
       </c>
       <c r="E23" s="1">
-        <v>27489</v>
+        <v>31887</v>
       </c>
       <c r="F23" s="1">
-        <v>44503</v>
+        <v>44490</v>
       </c>
       <c r="G23" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <v>35</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="J23" s="4">
-        <v>20000</v>
+        <v>70034</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E24" s="1">
-        <v>32912</v>
+        <v>32646</v>
       </c>
       <c r="F24" s="1">
-        <v>44504</v>
+        <v>44492</v>
       </c>
       <c r="G24" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <v>33</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="J24" s="4">
-        <v>20000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E25" s="1">
-        <v>29576</v>
+        <v>27847</v>
       </c>
       <c r="F25" s="1">
-        <v>44505</v>
+        <v>44494</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <v>46</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J25" s="4">
-        <v>31000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="1">
-        <v>28784</v>
+        <v>33082</v>
       </c>
       <c r="F26" s="1">
-        <v>44506</v>
+        <v>44495</v>
       </c>
       <c r="G26" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <v>32</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J26" s="4">
-        <v>100000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="1">
-        <v>28136</v>
+        <v>28967</v>
       </c>
       <c r="F27" s="1">
-        <v>44507</v>
+        <v>44496</v>
       </c>
       <c r="G27" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <v>43</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J27" s="4">
-        <v>40000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="1">
-        <v>30702</v>
+        <v>30813</v>
       </c>
       <c r="F28" s="1">
-        <v>44508</v>
+        <v>44497</v>
       </c>
       <c r="G28" s="5">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
         <v>38</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J28" s="4">
-        <v>100000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="1">
-        <v>28388</v>
+        <v>30716</v>
       </c>
       <c r="F29" s="1">
-        <v>44509</v>
+        <v>44499</v>
       </c>
       <c r="G29" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <v>38</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J29" s="4">
         <v>20000</v>
@@ -10196,65 +10209,65 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E30" s="1">
-        <v>33174</v>
+        <v>28208</v>
       </c>
       <c r="F30" s="1">
-        <v>44510</v>
+        <v>44500</v>
       </c>
       <c r="G30" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <v>45</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J30" s="4">
-        <v>21310</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E31" s="1">
-        <v>31904</v>
+        <v>29576</v>
       </c>
       <c r="F31" s="1">
-        <v>44511</v>
+        <v>44505</v>
       </c>
       <c r="G31" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <v>42</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J31" s="4">
         <v>31000</v>
@@ -10262,32 +10275,32 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="1">
-        <v>29561</v>
+        <v>28784</v>
       </c>
       <c r="F32" s="1">
-        <v>44512</v>
+        <v>44506</v>
       </c>
       <c r="G32" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <v>44</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J32" s="4">
         <v>100000</v>
@@ -10295,32 +10308,32 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E33" s="1">
-        <v>33214</v>
+        <v>30702</v>
       </c>
       <c r="F33" s="1">
-        <v>44513</v>
+        <v>44508</v>
       </c>
       <c r="G33" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <v>38</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J33" s="4">
         <v>100000</v>
@@ -10328,125 +10341,125 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E34" s="1">
-        <v>28186</v>
+        <v>28388</v>
       </c>
       <c r="F34" s="1">
-        <v>44514</v>
+        <v>44509</v>
       </c>
       <c r="G34" s="5">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
         <v>45</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J34" s="4">
-        <v>31000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E35" s="1">
-        <v>29857</v>
+        <v>33174</v>
       </c>
       <c r="F35" s="1">
-        <v>44515</v>
+        <v>44510</v>
       </c>
       <c r="G35" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <v>32</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J35" s="4">
-        <v>31000</v>
+        <v>21310</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E36" s="1">
-        <v>28780</v>
+        <v>31904</v>
       </c>
       <c r="F36" s="1">
-        <v>44516</v>
+        <v>44511</v>
       </c>
       <c r="G36" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <v>35</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J36" s="4">
-        <v>20000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="1">
-        <v>33678</v>
+        <v>29561</v>
       </c>
       <c r="F37" s="1">
-        <v>44517</v>
+        <v>44512</v>
       </c>
       <c r="G37" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <v>42</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>133</v>
@@ -10455,262 +10468,262 @@
         <v>138</v>
       </c>
       <c r="J37" s="4">
-        <v>20000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="1">
-        <v>30463</v>
+        <v>28186</v>
       </c>
       <c r="F38" s="1">
-        <v>44518</v>
+        <v>44514</v>
       </c>
       <c r="G38" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <v>45</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J38" s="4">
-        <v>20000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E39" s="1">
-        <v>32382</v>
+        <v>29857</v>
       </c>
       <c r="F39" s="1">
-        <v>44519</v>
+        <v>44515</v>
       </c>
       <c r="G39" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <v>41</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J39" s="4">
-        <v>70034</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E40" s="1">
-        <v>29547</v>
+        <v>28780</v>
       </c>
       <c r="F40" s="1">
-        <v>44520</v>
+        <v>44516</v>
       </c>
       <c r="G40" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <v>44</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J40" s="4">
-        <v>100000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="1">
-        <v>28277</v>
+        <v>33678</v>
       </c>
       <c r="F41" s="1">
-        <v>44521</v>
+        <v>44517</v>
       </c>
       <c r="G41" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <v>30</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J41" s="4">
-        <v>80000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="1">
-        <v>32297</v>
+        <v>30463</v>
       </c>
       <c r="F42" s="1">
-        <v>44522</v>
+        <v>44518</v>
       </c>
       <c r="G42" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <v>39</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J42" s="4">
-        <v>80000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E43" s="1">
-        <v>33771</v>
+        <v>29547</v>
       </c>
       <c r="F43" s="1">
-        <v>44523</v>
+        <v>44520</v>
       </c>
       <c r="G43" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <v>42</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="J43" s="4">
-        <v>70034</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="1">
-        <v>29038</v>
+        <v>28277</v>
       </c>
       <c r="F44" s="1">
-        <v>44524</v>
+        <v>44521</v>
       </c>
       <c r="G44" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <v>45</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J44" s="4">
-        <v>100000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="1">
-        <v>27732</v>
+        <v>32297</v>
       </c>
       <c r="F45" s="1">
-        <v>44525</v>
+        <v>44522</v>
       </c>
       <c r="G45" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <v>34</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>133</v>
@@ -10719,37 +10732,37 @@
         <v>137</v>
       </c>
       <c r="J45" s="4">
-        <v>100000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E46" s="1">
-        <v>29808</v>
+        <v>29038</v>
       </c>
       <c r="F46" s="1">
-        <v>44526</v>
+        <v>44524</v>
       </c>
       <c r="G46" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <v>43</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J46" s="4">
         <v>100000</v>
@@ -10757,26 +10770,26 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="1">
-        <v>29109</v>
+        <v>27732</v>
       </c>
       <c r="F47" s="1">
-        <v>44527</v>
+        <v>44525</v>
       </c>
       <c r="G47" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <v>47</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>133</v>
@@ -10785,73 +10798,73 @@
         <v>137</v>
       </c>
       <c r="J47" s="4">
-        <v>211000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E48" s="1">
-        <v>30009</v>
+        <v>29808</v>
       </c>
       <c r="F48" s="1">
-        <v>44528</v>
+        <v>44526</v>
       </c>
       <c r="G48" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <v>41</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="J48" s="4">
-        <v>70034</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="1">
-        <v>32293</v>
+        <v>29109</v>
       </c>
       <c r="F49" s="1">
-        <v>44529</v>
+        <v>44527</v>
       </c>
       <c r="G49" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <v>43</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J49" s="4">
-        <v>40000</v>
+        <v>211000</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -10874,7 +10887,7 @@
         <v>44530</v>
       </c>
       <c r="G50" s="5">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
         <v>37</v>
       </c>
       <c r="H50" s="4" t="s">
@@ -10888,6 +10901,1695 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:J50">
+    <sortCondition ref="H2:H50" customList="Клининг,Маркетинг,IT"/>
+  </sortState>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" hidden="1">
+      <c r="A2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>46</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J2" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" hidden="1">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G3" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>43</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J3" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G4" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <v>32</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J4" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" hidden="1">
+      <c r="A5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G5" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <v>45</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J5" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" hidden="1">
+      <c r="A6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G6" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <v>34</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J6" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" hidden="1">
+      <c r="A7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G7" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <v>34</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" hidden="1">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G8" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <v>36</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J8" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" hidden="1">
+      <c r="A9" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G9" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <v>37</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J9" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G10" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <v>30</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J10" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" hidden="1">
+      <c r="A11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G11" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <v>36</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J11" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" hidden="1">
+      <c r="A12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G12" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <v>40</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J12" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" hidden="1">
+      <c r="A13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G13" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <v>41</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J13" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" hidden="1">
+      <c r="A14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G14" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <v>47</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J14" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" hidden="1">
+      <c r="A15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G15" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <v>32</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J15" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" hidden="1">
+      <c r="A16" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G16" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <v>30</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" hidden="1">
+      <c r="A17" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G17" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <v>40</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J17" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" hidden="1">
+      <c r="A18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G18" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <v>38</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J18" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G19" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <v>32</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" hidden="1">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G20" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <v>36</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J20" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1">
+      <c r="A21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G21" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <v>30</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J21" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" hidden="1">
+      <c r="A22" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G22" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <v>40</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J22" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1">
+      <c r="A23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G23" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <v>35</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J23" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1">
+      <c r="A24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G24" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <v>33</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J24" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" hidden="1">
+      <c r="A25" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G25" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <v>46</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J25" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" hidden="1">
+      <c r="A26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G26" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <v>32</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J26" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" hidden="1">
+      <c r="A27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G27" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <v>43</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J27" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" hidden="1">
+      <c r="A28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G28" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <v>38</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J28" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" hidden="1">
+      <c r="A29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G29" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <v>38</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J29" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" hidden="1">
+      <c r="A30" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G30" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <v>45</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J30" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" hidden="1">
+      <c r="A31" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G31" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <v>42</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J31" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" hidden="1">
+      <c r="A32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G32" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <v>44</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J32" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" hidden="1">
+      <c r="A33" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G33" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <v>38</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J33" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" hidden="1">
+      <c r="A34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G34" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <v>45</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J34" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G35" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <v>32</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J35" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" hidden="1">
+      <c r="A36" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G36" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <v>35</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J36" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" hidden="1">
+      <c r="A37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G37" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <v>42</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J37" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" hidden="1">
+      <c r="A38" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G38" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <v>45</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J38" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" hidden="1">
+      <c r="A39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G39" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <v>41</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J39" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" hidden="1">
+      <c r="A40" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G40" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <v>44</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J40" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" hidden="1">
+      <c r="A41" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G41" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <v>30</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J41" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" hidden="1">
+      <c r="A42" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G42" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <v>39</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J42" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" hidden="1">
+      <c r="A43" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G43" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <v>42</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J43" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" hidden="1">
+      <c r="A44" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G44" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <v>45</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J44" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" hidden="1">
+      <c r="A45" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G45" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <v>34</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J45" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" hidden="1">
+      <c r="A46" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G46" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <v>43</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J46" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1">
+      <c r="A47" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G47" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <v>47</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J47" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" hidden="1">
+      <c r="A48" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G48" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <v>41</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J48" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" hidden="1">
+      <c r="A49" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G49" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <v>43</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J49" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" hidden="1">
+      <c r="A50" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G50" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <v>37</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J50" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J50">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="М"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="greaterThan" val="32906"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50">
       <formula1>"М, Ж"</formula1>

--- a/лаб.xlsx
+++ b/лаб.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="19155" windowHeight="11835" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="19155" windowHeight="11835" tabRatio="869" firstSheet="3" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="стандарт лист" sheetId="1" r:id="rId1"/>
@@ -14,16 +14,23 @@
     <sheet name="сортировка дата рождения" sheetId="5" r:id="rId5"/>
     <sheet name="особая сортировка по отделу" sheetId="6" r:id="rId6"/>
     <sheet name="Авто фильтр" sheetId="7" r:id="rId7"/>
+    <sheet name="Расширенный фильтр" sheetId="8" r:id="rId8"/>
+    <sheet name="Подведение промежуточных итогов" sheetId="9" r:id="rId9"/>
+    <sheet name=" Функции баз данных" sheetId="10" r:id="rId10"/>
+    <sheet name="Проверка вводимых данных" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Авто фильтр'!$A$1:$J$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Расширенный фильтр'!$A$1:$J$50</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="7">'Расширенный фильтр'!$M$6:$T$14</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="7">'Расширенный фильтр'!$M$1:$V$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3373" uniqueCount="165">
   <si>
     <t>Имя</t>
   </si>
@@ -489,6 +496,36 @@
   <si>
     <t>Даниилова</t>
   </si>
+  <si>
+    <t>М*</t>
+  </si>
+  <si>
+    <t>К*</t>
+  </si>
+  <si>
+    <t>Общий итог</t>
+  </si>
+  <si>
+    <t>IT Итог</t>
+  </si>
+  <si>
+    <t>Маркетинг Итог</t>
+  </si>
+  <si>
+    <t>Клининг Итог</t>
+  </si>
+  <si>
+    <t>IT Среднее</t>
+  </si>
+  <si>
+    <t>Маркетинг Среднее</t>
+  </si>
+  <si>
+    <t>Клининг Среднее</t>
+  </si>
+  <si>
+    <t>Общее среднее</t>
+  </si>
 </sst>
 </file>
 
@@ -497,7 +534,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,6 +544,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -536,7 +582,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -553,6 +599,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2526,6 +2578,3421 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:W50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" customWidth="1"/>
+    <col min="9" max="9" width="37.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="1"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>38</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G50" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>32</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J6" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J15" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J17" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J18" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J20" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J22" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G24" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J25" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G26" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G27" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G28" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G29" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J29" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J30" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G32" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J32" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G33" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J33" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J34" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G35" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J35" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G36" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J36" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G37" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J37" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G38" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J38" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G39" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J39" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G40" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J40" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G41" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J41" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J42" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G43" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J43" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G44" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J44" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G45" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J45" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G46" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J46" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G47" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J47" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G48" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J48" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G49" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J49" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G50" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J50" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50 Q1">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="34.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>38</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G3" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>32</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G4" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <v>36</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G5" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <v>36</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G6" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <v>30</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J6" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G7" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <v>37</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G8" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <v>30</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G9" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <v>40</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="4">
+        <v>21310</v>
+      </c>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G10" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <v>35</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G11" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <v>46</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G12" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <v>33</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G13" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <v>43</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G14" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <v>46</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G15" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <v>32</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J15" s="4">
+        <v>31000</v>
+      </c>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G16" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G17" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <v>38</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J17" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G18" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <v>36</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J18" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G19" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <v>38</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G20" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <v>45</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J20" s="4">
+        <v>31000</v>
+      </c>
+      <c r="M20" s="4"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G21" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <v>40</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="4">
+        <v>31000</v>
+      </c>
+      <c r="M21" s="4"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G22" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <v>41</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J22" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M22" s="4"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G23" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <v>47</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M23" s="4"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G24" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <v>32</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M24" s="4"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G25" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <v>42</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J25" s="4">
+        <v>31000</v>
+      </c>
+      <c r="M25" s="4"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G26" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <v>44</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M26" s="4"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G27" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <v>45</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" s="4">
+        <v>40000</v>
+      </c>
+      <c r="M27" s="4"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G28" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <v>38</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M28" s="4"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G29" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <v>45</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J29" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M29" s="4"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G30" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <v>32</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J30" s="4">
+        <v>21310</v>
+      </c>
+      <c r="M30" s="4"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G31" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <v>35</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" s="4">
+        <v>31000</v>
+      </c>
+      <c r="M31" s="4"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G32" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <v>42</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J32" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M32" s="4"/>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G33" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <v>32</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J33" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M33" s="4"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G34" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <v>45</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J34" s="4">
+        <v>31000</v>
+      </c>
+      <c r="M34" s="4"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G35" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <v>41</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J35" s="4">
+        <v>31000</v>
+      </c>
+      <c r="M35" s="4"/>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G36" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <v>44</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J36" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G37" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <v>30</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J37" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G38" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <v>39</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J38" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G39" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <v>34</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J39" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G40" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <v>42</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J40" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M40" s="4"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G41" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <v>45</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J41" s="4">
+        <v>80000</v>
+      </c>
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G42" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <v>34</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J42" s="4">
+        <v>80000</v>
+      </c>
+      <c r="M42" s="4"/>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G43" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <v>30</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J43" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G44" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <v>43</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J44" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G45" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <v>47</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J45" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G46" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <v>41</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J46" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G47" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <v>43</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J47" s="4">
+        <v>211000</v>
+      </c>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G48" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <v>40</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J48" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M48" s="4"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G49" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <v>34</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J49" s="4">
+        <v>40000</v>
+      </c>
+      <c r="M49" s="4"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G50" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <v>37</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J50" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Стой!" error="У нас такого отдела нет!" sqref="H2:H50">
+      <formula1>$M$1:$M$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J50"/>
@@ -4270,7 +7737,7 @@
         <v>44515</v>
       </c>
       <c r="G2" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <f t="shared" ref="G2:G33" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
         <v>41</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -4303,7 +7770,7 @@
         <v>44524</v>
       </c>
       <c r="G3" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -4336,7 +7803,7 @@
         <v>44485</v>
       </c>
       <c r="G4" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -4369,7 +7836,7 @@
         <v>44492</v>
       </c>
       <c r="G5" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>33</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -4402,7 +7869,7 @@
         <v>44523</v>
       </c>
       <c r="G6" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -4435,7 +7902,7 @@
         <v>44507</v>
       </c>
       <c r="G7" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -4468,7 +7935,7 @@
         <v>44495</v>
       </c>
       <c r="G8" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H8" s="4" t="s">
@@ -4501,7 +7968,7 @@
         <v>44488</v>
       </c>
       <c r="G9" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -4534,7 +8001,7 @@
         <v>44493</v>
       </c>
       <c r="G10" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -4567,7 +8034,7 @@
         <v>44522</v>
       </c>
       <c r="G11" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -4600,7 +8067,7 @@
         <v>44520</v>
       </c>
       <c r="G12" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -4633,7 +8100,7 @@
         <v>44509</v>
       </c>
       <c r="G13" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -4666,7 +8133,7 @@
         <v>44526</v>
       </c>
       <c r="G14" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -4699,7 +8166,7 @@
         <v>44500</v>
       </c>
       <c r="G15" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -4732,7 +8199,7 @@
         <v>44512</v>
       </c>
       <c r="G16" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -4765,7 +8232,7 @@
         <v>44503</v>
       </c>
       <c r="G17" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>47</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -4798,7 +8265,7 @@
         <v>44514</v>
       </c>
       <c r="G18" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -4831,7 +8298,7 @@
         <v>44521</v>
       </c>
       <c r="G19" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -4864,7 +8331,7 @@
         <v>44482</v>
       </c>
       <c r="G20" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -4897,7 +8364,7 @@
         <v>44499</v>
       </c>
       <c r="G21" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -4930,7 +8397,7 @@
         <v>44496</v>
       </c>
       <c r="G22" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -4963,7 +8430,7 @@
         <v>44484</v>
       </c>
       <c r="G23" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -4996,7 +8463,7 @@
         <v>44513</v>
       </c>
       <c r="G24" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -5029,7 +8496,7 @@
         <v>44487</v>
       </c>
       <c r="G25" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -5062,7 +8529,7 @@
         <v>44525</v>
       </c>
       <c r="G26" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>47</v>
       </c>
       <c r="H26" s="4" t="s">
@@ -5095,7 +8562,7 @@
         <v>44529</v>
       </c>
       <c r="G27" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -5128,7 +8595,7 @@
         <v>44494</v>
       </c>
       <c r="G28" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>46</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -5161,7 +8628,7 @@
         <v>44490</v>
       </c>
       <c r="G29" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>35</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -5194,7 +8661,7 @@
         <v>44502</v>
       </c>
       <c r="G30" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -5227,7 +8694,7 @@
         <v>44508</v>
       </c>
       <c r="G31" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H31" s="4" t="s">
@@ -5260,7 +8727,7 @@
         <v>44519</v>
       </c>
       <c r="G32" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H32" s="4" t="s">
@@ -5293,7 +8760,7 @@
         <v>44510</v>
       </c>
       <c r="G33" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H33" s="4" t="s">
@@ -5326,7 +8793,7 @@
         <v>44517</v>
       </c>
       <c r="G34" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <f t="shared" ref="G34:G50" ca="1" si="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
         <v>30</v>
       </c>
       <c r="H34" s="4" t="s">
@@ -5359,7 +8826,7 @@
         <v>44511</v>
       </c>
       <c r="G35" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="H35" s="4" t="s">
@@ -5392,7 +8859,7 @@
         <v>44518</v>
       </c>
       <c r="G36" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>39</v>
       </c>
       <c r="H36" s="4" t="s">
@@ -5425,7 +8892,7 @@
         <v>44498</v>
       </c>
       <c r="G37" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>36</v>
       </c>
       <c r="H37" s="4" t="s">
@@ -5458,7 +8925,7 @@
         <v>44527</v>
       </c>
       <c r="G38" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>43</v>
       </c>
       <c r="H38" s="4" t="s">
@@ -5491,7 +8958,7 @@
         <v>44489</v>
       </c>
       <c r="G39" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>40</v>
       </c>
       <c r="H39" s="4" t="s">
@@ -5524,7 +8991,7 @@
         <v>44486</v>
       </c>
       <c r="G40" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>30</v>
       </c>
       <c r="H40" s="4" t="s">
@@ -5557,7 +9024,7 @@
         <v>44528</v>
       </c>
       <c r="G41" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>40</v>
       </c>
       <c r="H41" s="4" t="s">
@@ -5590,7 +9057,7 @@
         <v>44483</v>
       </c>
       <c r="G42" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H42" s="4" t="s">
@@ -5623,7 +9090,7 @@
         <v>44497</v>
       </c>
       <c r="G43" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>38</v>
       </c>
       <c r="H43" s="4" t="s">
@@ -5656,7 +9123,7 @@
         <v>44504</v>
       </c>
       <c r="G44" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H44" s="4" t="s">
@@ -5689,7 +9156,7 @@
         <v>44501</v>
       </c>
       <c r="G45" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>40</v>
       </c>
       <c r="H45" s="4" t="s">
@@ -5722,7 +9189,7 @@
         <v>44506</v>
       </c>
       <c r="G46" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>44</v>
       </c>
       <c r="H46" s="4" t="s">
@@ -5755,7 +9222,7 @@
         <v>44530</v>
       </c>
       <c r="G47" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>37</v>
       </c>
       <c r="H47" s="4" t="s">
@@ -5788,7 +9255,7 @@
         <v>44491</v>
       </c>
       <c r="G48" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>46</v>
       </c>
       <c r="H48" s="4" t="s">
@@ -5821,7 +9288,7 @@
         <v>44505</v>
       </c>
       <c r="G49" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>42</v>
       </c>
       <c r="H49" s="4" t="s">
@@ -5854,7 +9321,7 @@
         <v>44516</v>
       </c>
       <c r="G50" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>44</v>
       </c>
       <c r="H50" s="4" t="s">
@@ -5947,7 +9414,7 @@
         <v>44516</v>
       </c>
       <c r="G2" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <f t="shared" ref="G2:G33" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
         <v>44</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -5980,7 +9447,7 @@
         <v>44489</v>
       </c>
       <c r="G3" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -6013,7 +9480,7 @@
         <v>44506</v>
       </c>
       <c r="G4" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>44</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -6046,7 +9513,7 @@
         <v>44524</v>
       </c>
       <c r="G5" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -6079,7 +9546,7 @@
         <v>44502</v>
       </c>
       <c r="G6" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -6112,7 +9579,7 @@
         <v>44515</v>
       </c>
       <c r="G7" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -6145,7 +9612,7 @@
         <v>44520</v>
       </c>
       <c r="G8" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H8" s="4" t="s">
@@ -6178,7 +9645,7 @@
         <v>44493</v>
       </c>
       <c r="G9" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -6211,7 +9678,7 @@
         <v>44507</v>
       </c>
       <c r="G10" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -6244,7 +9711,7 @@
         <v>44499</v>
       </c>
       <c r="G11" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -6277,7 +9744,7 @@
         <v>44526</v>
       </c>
       <c r="G12" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -6310,7 +9777,7 @@
         <v>44527</v>
       </c>
       <c r="G13" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -6343,7 +9810,7 @@
         <v>44496</v>
       </c>
       <c r="G14" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -6376,7 +9843,7 @@
         <v>44482</v>
       </c>
       <c r="G15" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -6409,7 +9876,7 @@
         <v>44500</v>
       </c>
       <c r="G16" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -6442,7 +9909,7 @@
         <v>44488</v>
       </c>
       <c r="G17" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -6475,7 +9942,7 @@
         <v>44497</v>
       </c>
       <c r="G18" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -6508,7 +9975,7 @@
         <v>44513</v>
       </c>
       <c r="G19" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -6541,7 +10008,7 @@
         <v>44528</v>
       </c>
       <c r="G20" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -6574,7 +10041,7 @@
         <v>44487</v>
       </c>
       <c r="G21" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -6607,7 +10074,7 @@
         <v>44517</v>
       </c>
       <c r="G22" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -6640,7 +10107,7 @@
         <v>44519</v>
       </c>
       <c r="G23" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -6673,7 +10140,7 @@
         <v>44523</v>
       </c>
       <c r="G24" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -6706,7 +10173,7 @@
         <v>44509</v>
       </c>
       <c r="G25" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -6739,7 +10206,7 @@
         <v>44505</v>
       </c>
       <c r="G26" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H26" s="4" t="s">
@@ -6772,7 +10239,7 @@
         <v>44510</v>
       </c>
       <c r="G27" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -6805,7 +10272,7 @@
         <v>44486</v>
       </c>
       <c r="G28" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -6838,7 +10305,7 @@
         <v>44504</v>
       </c>
       <c r="G29" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -6871,7 +10338,7 @@
         <v>44484</v>
       </c>
       <c r="G30" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -6904,7 +10371,7 @@
         <v>44508</v>
       </c>
       <c r="G31" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H31" s="4" t="s">
@@ -6937,7 +10404,7 @@
         <v>44485</v>
       </c>
       <c r="G32" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H32" s="4" t="s">
@@ -6970,7 +10437,7 @@
         <v>44512</v>
       </c>
       <c r="G33" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H33" s="4" t="s">
@@ -7003,7 +10470,7 @@
         <v>44514</v>
       </c>
       <c r="G34" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <f t="shared" ref="G34:G50" ca="1" si="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
         <v>45</v>
       </c>
       <c r="H34" s="4" t="s">
@@ -7036,7 +10503,7 @@
         <v>44521</v>
       </c>
       <c r="G35" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>45</v>
       </c>
       <c r="H35" s="4" t="s">
@@ -7069,7 +10536,7 @@
         <v>44530</v>
       </c>
       <c r="G36" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>37</v>
       </c>
       <c r="H36" s="4" t="s">
@@ -7102,7 +10569,7 @@
         <v>44495</v>
       </c>
       <c r="G37" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H37" s="4" t="s">
@@ -7135,7 +10602,7 @@
         <v>44522</v>
       </c>
       <c r="G38" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>34</v>
       </c>
       <c r="H38" s="4" t="s">
@@ -7168,7 +10635,7 @@
         <v>44490</v>
       </c>
       <c r="G39" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="H39" s="4" t="s">
@@ -7201,7 +10668,7 @@
         <v>44503</v>
       </c>
       <c r="G40" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>47</v>
       </c>
       <c r="H40" s="4" t="s">
@@ -7234,7 +10701,7 @@
         <v>44501</v>
       </c>
       <c r="G41" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>40</v>
       </c>
       <c r="H41" s="4" t="s">
@@ -7267,7 +10734,7 @@
         <v>44511</v>
       </c>
       <c r="G42" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="H42" s="4" t="s">
@@ -7300,7 +10767,7 @@
         <v>44483</v>
       </c>
       <c r="G43" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H43" s="4" t="s">
@@ -7333,7 +10800,7 @@
         <v>44492</v>
       </c>
       <c r="G44" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>33</v>
       </c>
       <c r="H44" s="4" t="s">
@@ -7366,7 +10833,7 @@
         <v>44525</v>
       </c>
       <c r="G45" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>47</v>
       </c>
       <c r="H45" s="4" t="s">
@@ -7399,7 +10866,7 @@
         <v>44518</v>
       </c>
       <c r="G46" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>39</v>
       </c>
       <c r="H46" s="4" t="s">
@@ -7432,7 +10899,7 @@
         <v>44491</v>
       </c>
       <c r="G47" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>46</v>
       </c>
       <c r="H47" s="4" t="s">
@@ -7465,7 +10932,7 @@
         <v>44498</v>
       </c>
       <c r="G48" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>36</v>
       </c>
       <c r="H48" s="4" t="s">
@@ -7498,7 +10965,7 @@
         <v>44529</v>
       </c>
       <c r="G49" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>34</v>
       </c>
       <c r="H49" s="4" t="s">
@@ -7531,7 +10998,7 @@
         <v>44494</v>
       </c>
       <c r="G50" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>46</v>
       </c>
       <c r="H50" s="4" t="s">
@@ -9303,7 +12770,7 @@
         <v>44491</v>
       </c>
       <c r="G2" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <f t="shared" ref="G2:G33" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
         <v>46</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -9336,7 +12803,7 @@
         <v>44493</v>
       </c>
       <c r="G3" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -9369,7 +12836,7 @@
         <v>44504</v>
       </c>
       <c r="G4" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -9402,7 +12869,7 @@
         <v>44507</v>
       </c>
       <c r="G5" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -9435,7 +12902,7 @@
         <v>44519</v>
       </c>
       <c r="G6" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -9468,7 +12935,7 @@
         <v>44529</v>
       </c>
       <c r="G7" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -9501,7 +12968,7 @@
         <v>44485</v>
       </c>
       <c r="G8" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H8" s="4" t="s">
@@ -9534,7 +13001,7 @@
         <v>44487</v>
       </c>
       <c r="G9" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -9567,7 +13034,7 @@
         <v>44488</v>
       </c>
       <c r="G10" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -9600,7 +13067,7 @@
         <v>44498</v>
       </c>
       <c r="G11" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -9633,7 +13100,7 @@
         <v>44501</v>
       </c>
       <c r="G12" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -9666,7 +13133,7 @@
         <v>44502</v>
       </c>
       <c r="G13" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -9699,7 +13166,7 @@
         <v>44503</v>
       </c>
       <c r="G14" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>47</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -9732,7 +13199,7 @@
         <v>44513</v>
       </c>
       <c r="G15" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -9765,7 +13232,7 @@
         <v>44523</v>
       </c>
       <c r="G16" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -9798,7 +13265,7 @@
         <v>44528</v>
       </c>
       <c r="G17" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -9831,7 +13298,7 @@
         <v>44482</v>
       </c>
       <c r="G18" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -9864,7 +13331,7 @@
         <v>44483</v>
       </c>
       <c r="G19" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -9897,7 +13364,7 @@
         <v>44484</v>
       </c>
       <c r="G20" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -9930,7 +13397,7 @@
         <v>44486</v>
       </c>
       <c r="G21" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -9963,7 +13430,7 @@
         <v>44489</v>
       </c>
       <c r="G22" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -9996,7 +13463,7 @@
         <v>44490</v>
       </c>
       <c r="G23" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>35</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -10029,7 +13496,7 @@
         <v>44492</v>
       </c>
       <c r="G24" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>33</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -10062,7 +13529,7 @@
         <v>44494</v>
       </c>
       <c r="G25" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>46</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -10095,7 +13562,7 @@
         <v>44495</v>
       </c>
       <c r="G26" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H26" s="4" t="s">
@@ -10128,7 +13595,7 @@
         <v>44496</v>
       </c>
       <c r="G27" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -10161,7 +13628,7 @@
         <v>44497</v>
       </c>
       <c r="G28" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -10194,7 +13661,7 @@
         <v>44499</v>
       </c>
       <c r="G29" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -10227,7 +13694,7 @@
         <v>44500</v>
       </c>
       <c r="G30" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -10260,7 +13727,7 @@
         <v>44505</v>
       </c>
       <c r="G31" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H31" s="4" t="s">
@@ -10293,7 +13760,7 @@
         <v>44506</v>
       </c>
       <c r="G32" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>44</v>
       </c>
       <c r="H32" s="4" t="s">
@@ -10326,7 +13793,7 @@
         <v>44508</v>
       </c>
       <c r="G33" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H33" s="4" t="s">
@@ -10359,7 +13826,7 @@
         <v>44509</v>
       </c>
       <c r="G34" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <f t="shared" ref="G34:G50" ca="1" si="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
         <v>45</v>
       </c>
       <c r="H34" s="4" t="s">
@@ -10392,7 +13859,7 @@
         <v>44510</v>
       </c>
       <c r="G35" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H35" s="4" t="s">
@@ -10425,7 +13892,7 @@
         <v>44511</v>
       </c>
       <c r="G36" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="H36" s="4" t="s">
@@ -10458,7 +13925,7 @@
         <v>44512</v>
       </c>
       <c r="G37" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>42</v>
       </c>
       <c r="H37" s="4" t="s">
@@ -10491,7 +13958,7 @@
         <v>44514</v>
       </c>
       <c r="G38" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>45</v>
       </c>
       <c r="H38" s="4" t="s">
@@ -10524,7 +13991,7 @@
         <v>44515</v>
       </c>
       <c r="G39" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
       <c r="H39" s="4" t="s">
@@ -10557,7 +14024,7 @@
         <v>44516</v>
       </c>
       <c r="G40" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>44</v>
       </c>
       <c r="H40" s="4" t="s">
@@ -10590,7 +14057,7 @@
         <v>44517</v>
       </c>
       <c r="G41" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>30</v>
       </c>
       <c r="H41" s="4" t="s">
@@ -10623,7 +14090,7 @@
         <v>44518</v>
       </c>
       <c r="G42" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>39</v>
       </c>
       <c r="H42" s="4" t="s">
@@ -10656,7 +14123,7 @@
         <v>44520</v>
       </c>
       <c r="G43" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>42</v>
       </c>
       <c r="H43" s="4" t="s">
@@ -10689,7 +14156,7 @@
         <v>44521</v>
       </c>
       <c r="G44" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>45</v>
       </c>
       <c r="H44" s="4" t="s">
@@ -10722,7 +14189,7 @@
         <v>44522</v>
       </c>
       <c r="G45" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>34</v>
       </c>
       <c r="H45" s="4" t="s">
@@ -10755,7 +14222,7 @@
         <v>44524</v>
       </c>
       <c r="G46" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>43</v>
       </c>
       <c r="H46" s="4" t="s">
@@ -10788,7 +14255,7 @@
         <v>44525</v>
       </c>
       <c r="G47" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>47</v>
       </c>
       <c r="H47" s="4" t="s">
@@ -10821,7 +14288,7 @@
         <v>44526</v>
       </c>
       <c r="G48" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
       <c r="H48" s="4" t="s">
@@ -10854,7 +14321,7 @@
         <v>44527</v>
       </c>
       <c r="G49" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>43</v>
       </c>
       <c r="H49" s="4" t="s">
@@ -10887,7 +14354,7 @@
         <v>44530</v>
       </c>
       <c r="G50" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>37</v>
       </c>
       <c r="H50" s="4" t="s">
@@ -10980,7 +14447,7 @@
         <v>44491</v>
       </c>
       <c r="G2" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <f t="shared" ref="G2:G33" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
         <v>46</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -11013,7 +14480,7 @@
         <v>44493</v>
       </c>
       <c r="G3" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -11046,7 +14513,7 @@
         <v>44504</v>
       </c>
       <c r="G4" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -11079,7 +14546,7 @@
         <v>44507</v>
       </c>
       <c r="G5" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -11112,7 +14579,7 @@
         <v>44519</v>
       </c>
       <c r="G6" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -11145,7 +14612,7 @@
         <v>44529</v>
       </c>
       <c r="G7" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -11178,7 +14645,7 @@
         <v>44485</v>
       </c>
       <c r="G8" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H8" s="4" t="s">
@@ -11211,7 +14678,7 @@
         <v>44487</v>
       </c>
       <c r="G9" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -11244,7 +14711,7 @@
         <v>44488</v>
       </c>
       <c r="G10" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -11277,7 +14744,7 @@
         <v>44498</v>
       </c>
       <c r="G11" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -11310,7 +14777,7 @@
         <v>44501</v>
       </c>
       <c r="G12" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -11343,7 +14810,7 @@
         <v>44502</v>
       </c>
       <c r="G13" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>41</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -11376,7 +14843,7 @@
         <v>44503</v>
       </c>
       <c r="G14" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>47</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -11409,7 +14876,7 @@
         <v>44513</v>
       </c>
       <c r="G15" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -11442,7 +14909,7 @@
         <v>44523</v>
       </c>
       <c r="G16" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -11475,7 +14942,7 @@
         <v>44528</v>
       </c>
       <c r="G17" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -11508,7 +14975,7 @@
         <v>44482</v>
       </c>
       <c r="G18" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -11541,7 +15008,7 @@
         <v>44483</v>
       </c>
       <c r="G19" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -11574,7 +15041,7 @@
         <v>44484</v>
       </c>
       <c r="G20" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -11607,7 +15074,7 @@
         <v>44486</v>
       </c>
       <c r="G21" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -11640,7 +15107,7 @@
         <v>44489</v>
       </c>
       <c r="G22" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>40</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -11673,7 +15140,7 @@
         <v>44490</v>
       </c>
       <c r="G23" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>35</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -11706,7 +15173,7 @@
         <v>44492</v>
       </c>
       <c r="G24" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>33</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -11739,7 +15206,7 @@
         <v>44494</v>
       </c>
       <c r="G25" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>46</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -11772,7 +15239,7 @@
         <v>44495</v>
       </c>
       <c r="G26" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>32</v>
       </c>
       <c r="H26" s="4" t="s">
@@ -11805,7 +15272,7 @@
         <v>44496</v>
       </c>
       <c r="G27" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -11838,7 +15305,7 @@
         <v>44497</v>
       </c>
       <c r="G28" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -11871,7 +15338,7 @@
         <v>44499</v>
       </c>
       <c r="G29" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -11904,7 +15371,7 @@
         <v>44500</v>
       </c>
       <c r="G30" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>45</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -11937,7 +15404,7 @@
         <v>44505</v>
       </c>
       <c r="G31" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>42</v>
       </c>
       <c r="H31" s="4" t="s">
@@ -11970,7 +15437,7 @@
         <v>44506</v>
       </c>
       <c r="G32" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>44</v>
       </c>
       <c r="H32" s="4" t="s">
@@ -12003,7 +15470,7 @@
         <v>44508</v>
       </c>
       <c r="G33" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>38</v>
       </c>
       <c r="H33" s="4" t="s">
@@ -12036,7 +15503,7 @@
         <v>44509</v>
       </c>
       <c r="G34" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <f t="shared" ref="G34:G50" ca="1" si="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
         <v>45</v>
       </c>
       <c r="H34" s="4" t="s">
@@ -12069,7 +15536,7 @@
         <v>44510</v>
       </c>
       <c r="G35" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E35))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>32</v>
       </c>
       <c r="H35" s="4" t="s">
@@ -12102,7 +15569,7 @@
         <v>44511</v>
       </c>
       <c r="G36" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E36))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="H36" s="4" t="s">
@@ -12135,7 +15602,7 @@
         <v>44512</v>
       </c>
       <c r="G37" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>42</v>
       </c>
       <c r="H37" s="4" t="s">
@@ -12168,7 +15635,7 @@
         <v>44514</v>
       </c>
       <c r="G38" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>45</v>
       </c>
       <c r="H38" s="4" t="s">
@@ -12201,7 +15668,7 @@
         <v>44515</v>
       </c>
       <c r="G39" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
       <c r="H39" s="4" t="s">
@@ -12234,7 +15701,7 @@
         <v>44516</v>
       </c>
       <c r="G40" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>44</v>
       </c>
       <c r="H40" s="4" t="s">
@@ -12267,7 +15734,7 @@
         <v>44517</v>
       </c>
       <c r="G41" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>30</v>
       </c>
       <c r="H41" s="4" t="s">
@@ -12300,7 +15767,7 @@
         <v>44518</v>
       </c>
       <c r="G42" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>39</v>
       </c>
       <c r="H42" s="4" t="s">
@@ -12333,7 +15800,7 @@
         <v>44520</v>
       </c>
       <c r="G43" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E43))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>42</v>
       </c>
       <c r="H43" s="4" t="s">
@@ -12366,7 +15833,7 @@
         <v>44521</v>
       </c>
       <c r="G44" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E44))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>45</v>
       </c>
       <c r="H44" s="4" t="s">
@@ -12399,7 +15866,7 @@
         <v>44522</v>
       </c>
       <c r="G45" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>34</v>
       </c>
       <c r="H45" s="4" t="s">
@@ -12432,7 +15899,7 @@
         <v>44524</v>
       </c>
       <c r="G46" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>43</v>
       </c>
       <c r="H46" s="4" t="s">
@@ -12465,7 +15932,7 @@
         <v>44525</v>
       </c>
       <c r="G47" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>47</v>
       </c>
       <c r="H47" s="4" t="s">
@@ -12498,7 +15965,7 @@
         <v>44526</v>
       </c>
       <c r="G48" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
       <c r="H48" s="4" t="s">
@@ -12531,7 +15998,7 @@
         <v>44527</v>
       </c>
       <c r="G49" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>43</v>
       </c>
       <c r="H49" s="4" t="s">
@@ -12564,7 +16031,7 @@
         <v>44530</v>
       </c>
       <c r="G50" s="5">
-        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>37</v>
       </c>
       <c r="H50" s="4" t="s">
@@ -12597,4 +16064,3616 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:V50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" customWidth="1"/>
+    <col min="9" max="9" width="27.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>38</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G50" ca="1" si="0">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>32</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="P3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J6" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="4"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="4"/>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="4"/>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="4">
+        <v>21310</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="4"/>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="4"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="4"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="4"/>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="4">
+        <v>70034</v>
+      </c>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="4"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="4">
+        <v>100000</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="4"/>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J15" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J17" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J18" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J20" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J22" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G24" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J25" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G26" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G27" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G28" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G29" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J29" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J30" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G32" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J32" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G33" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J33" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J34" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G35" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J35" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G36" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J36" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G37" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J37" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G38" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J38" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G39" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J39" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G40" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J40" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G41" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J41" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J42" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G43" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J43" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G44" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J44" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G45" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J45" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G46" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J46" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G47" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J47" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G48" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J48" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G49" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J49" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G50" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J50" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D50 O6 P1">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J58"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="9" max="9" width="37.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" outlineLevel="3">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30722</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44482</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E2))</f>
+        <v>38</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" outlineLevel="3">
+      <c r="A3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2">
+        <v>33057</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44483</v>
+      </c>
+      <c r="G3" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E3))</f>
+        <v>32</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" outlineLevel="3">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>31518</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44484</v>
+      </c>
+      <c r="G4" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E4))</f>
+        <v>36</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" outlineLevel="3">
+      <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
+        <v>33806</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44486</v>
+      </c>
+      <c r="G5" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E5))</f>
+        <v>30</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" outlineLevel="3">
+      <c r="A6" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30198</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44489</v>
+      </c>
+      <c r="G6" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E6))</f>
+        <v>40</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" outlineLevel="3">
+      <c r="A7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1">
+        <v>31887</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44490</v>
+      </c>
+      <c r="G7" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E7))</f>
+        <v>35</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J7" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" outlineLevel="3">
+      <c r="A8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1">
+        <v>32646</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44492</v>
+      </c>
+      <c r="G8" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E8))</f>
+        <v>33</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" outlineLevel="3">
+      <c r="A9" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1">
+        <v>27847</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44494</v>
+      </c>
+      <c r="G9" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E9))</f>
+        <v>46</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" outlineLevel="3">
+      <c r="A10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1">
+        <v>33082</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44495</v>
+      </c>
+      <c r="G10" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E10))</f>
+        <v>32</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J10" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" outlineLevel="3">
+      <c r="A11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1">
+        <v>28967</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44496</v>
+      </c>
+      <c r="G11" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E11))</f>
+        <v>43</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J11" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" outlineLevel="3">
+      <c r="A12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1">
+        <v>30813</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44497</v>
+      </c>
+      <c r="G12" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E12))</f>
+        <v>38</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J12" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" outlineLevel="3">
+      <c r="A13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1">
+        <v>30716</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44499</v>
+      </c>
+      <c r="G13" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E13))</f>
+        <v>38</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J13" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" outlineLevel="3">
+      <c r="A14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1">
+        <v>28208</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44500</v>
+      </c>
+      <c r="G14" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E14))</f>
+        <v>45</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J14" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" outlineLevel="3">
+      <c r="A15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="1">
+        <v>29576</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44505</v>
+      </c>
+      <c r="G15" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E15))</f>
+        <v>42</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J15" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" outlineLevel="3">
+      <c r="A16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>28784</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44506</v>
+      </c>
+      <c r="G16" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E16))</f>
+        <v>44</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J16" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" outlineLevel="3">
+      <c r="A17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1">
+        <v>30702</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44508</v>
+      </c>
+      <c r="G17" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E17))</f>
+        <v>38</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" outlineLevel="3">
+      <c r="A18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1">
+        <v>28388</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44509</v>
+      </c>
+      <c r="G18" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E18))</f>
+        <v>45</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J18" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" outlineLevel="3">
+      <c r="A19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>33174</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44510</v>
+      </c>
+      <c r="G19" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E19))</f>
+        <v>32</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" outlineLevel="3">
+      <c r="A20" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>31904</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44511</v>
+      </c>
+      <c r="G20" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E20))</f>
+        <v>35</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J20" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" outlineLevel="3">
+      <c r="A21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1">
+        <v>29561</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44512</v>
+      </c>
+      <c r="G21" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E21))</f>
+        <v>42</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J21" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" outlineLevel="3">
+      <c r="A22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="1">
+        <v>28186</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44514</v>
+      </c>
+      <c r="G22" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E22))</f>
+        <v>45</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J22" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" outlineLevel="3">
+      <c r="A23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1">
+        <v>29857</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44515</v>
+      </c>
+      <c r="G23" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E23))</f>
+        <v>41</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J23" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" outlineLevel="3">
+      <c r="A24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1">
+        <v>28780</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44516</v>
+      </c>
+      <c r="G24" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E24))</f>
+        <v>44</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J24" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" outlineLevel="3">
+      <c r="A25" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="1">
+        <v>33678</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44517</v>
+      </c>
+      <c r="G25" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E25))</f>
+        <v>30</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J25" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" outlineLevel="3">
+      <c r="A26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1">
+        <v>30463</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44518</v>
+      </c>
+      <c r="G26" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E26))</f>
+        <v>39</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" outlineLevel="3">
+      <c r="A27" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="1">
+        <v>29547</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44520</v>
+      </c>
+      <c r="G27" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E27))</f>
+        <v>42</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" outlineLevel="3">
+      <c r="A28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1">
+        <v>28277</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44521</v>
+      </c>
+      <c r="G28" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E28))</f>
+        <v>45</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" outlineLevel="3">
+      <c r="A29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="1">
+        <v>32297</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44522</v>
+      </c>
+      <c r="G29" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E29))</f>
+        <v>34</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J29" s="4">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" outlineLevel="3">
+      <c r="A30" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1">
+        <v>29038</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44524</v>
+      </c>
+      <c r="G30" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E30))</f>
+        <v>43</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J30" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" outlineLevel="3">
+      <c r="A31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>27732</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44525</v>
+      </c>
+      <c r="G31" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E31))</f>
+        <v>47</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J31" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" outlineLevel="3">
+      <c r="A32" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="1">
+        <v>29808</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44526</v>
+      </c>
+      <c r="G32" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E32))</f>
+        <v>41</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J32" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" outlineLevel="3">
+      <c r="A33" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1">
+        <v>29109</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44527</v>
+      </c>
+      <c r="G33" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E33))</f>
+        <v>43</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J33" s="4">
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" outlineLevel="3">
+      <c r="A34" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1">
+        <v>31213</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44530</v>
+      </c>
+      <c r="G34" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E34))</f>
+        <v>37</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J34" s="4">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" outlineLevel="2">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4">
+        <f>SUBTOTAL(1,J2:J34)</f>
+        <v>58818.121212121216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" outlineLevel="1">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4">
+        <f>SUBTOTAL(9,J2:J34)</f>
+        <v>1940998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" outlineLevel="3">
+      <c r="A37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="1">
+        <v>28013</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G37" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E37))</f>
+        <v>46</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J37" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" outlineLevel="3">
+      <c r="A38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="1">
+        <v>29013</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44493</v>
+      </c>
+      <c r="G38" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E38))</f>
+        <v>43</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J38" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" outlineLevel="3">
+      <c r="A39" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1">
+        <v>32912</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44504</v>
+      </c>
+      <c r="G39" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E39))</f>
+        <v>32</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J39" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" outlineLevel="3">
+      <c r="A40" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="1">
+        <v>28136</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44507</v>
+      </c>
+      <c r="G40" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E40))</f>
+        <v>45</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J40" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" outlineLevel="3">
+      <c r="A41" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="1">
+        <v>32382</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44519</v>
+      </c>
+      <c r="G41" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E41))</f>
+        <v>34</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J41" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" outlineLevel="3">
+      <c r="A42" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="1">
+        <v>32293</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44529</v>
+      </c>
+      <c r="G42" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E42))</f>
+        <v>34</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J42" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" outlineLevel="2">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4">
+        <f>SUBTOTAL(1,J37:J42)</f>
+        <v>51683.666666666664</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" outlineLevel="1">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4">
+        <f>SUBTOTAL(9,J37:J42)</f>
+        <v>310102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" outlineLevel="3">
+      <c r="A45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>31434</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44485</v>
+      </c>
+      <c r="G45" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E45))</f>
+        <v>36</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J45" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" outlineLevel="3">
+      <c r="A46" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1">
+        <v>31216</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44487</v>
+      </c>
+      <c r="G46" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E46))</f>
+        <v>37</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J46" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" outlineLevel="3">
+      <c r="A47" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="1">
+        <v>33856</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44488</v>
+      </c>
+      <c r="G47" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E47))</f>
+        <v>30</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J47" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" outlineLevel="3">
+      <c r="A48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1">
+        <v>31684</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44498</v>
+      </c>
+      <c r="G48" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E48))</f>
+        <v>36</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J48" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" outlineLevel="3">
+      <c r="A49" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1">
+        <v>30065</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44501</v>
+      </c>
+      <c r="G49" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E49))</f>
+        <v>40</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J49" s="4">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" outlineLevel="3">
+      <c r="A50" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="1">
+        <v>29640</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G50" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E50))</f>
+        <v>41</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J50" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" outlineLevel="3">
+      <c r="A51" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="1">
+        <v>27489</v>
+      </c>
+      <c r="F51" s="1">
+        <v>44503</v>
+      </c>
+      <c r="G51" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E51))</f>
+        <v>47</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J51" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" outlineLevel="3">
+      <c r="A52" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="1">
+        <v>33214</v>
+      </c>
+      <c r="F52" s="1">
+        <v>44513</v>
+      </c>
+      <c r="G52" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E52))</f>
+        <v>32</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J52" s="4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" outlineLevel="3">
+      <c r="A53" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="1">
+        <v>33771</v>
+      </c>
+      <c r="F53" s="1">
+        <v>44523</v>
+      </c>
+      <c r="G53" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E53))</f>
+        <v>30</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J53" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" outlineLevel="3">
+      <c r="A54" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="1">
+        <v>30009</v>
+      </c>
+      <c r="F54" s="1">
+        <v>44528</v>
+      </c>
+      <c r="G54" s="5">
+        <f ca="1">INT(YEAR(TODAY()))-INT(YEAR(E54))</f>
+        <v>40</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J54" s="4">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" outlineLevel="2">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4">
+        <f>SUBTOTAL(1,J45:J54)</f>
+        <v>49113.599999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" outlineLevel="1">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4">
+        <f>SUBTOTAL(9,J45:J54)</f>
+        <v>491136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4">
+        <f>SUBTOTAL(1,J2:J54)</f>
+        <v>55964</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4">
+        <f>SUBTOTAL(9,J2:J54)</f>
+        <v>2742236</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:J50">
+    <sortCondition ref="H1"/>
+  </sortState>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D37:D42 D1:D34 D45:D54">
+      <formula1>"М, Ж"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>